--- a/data/historicalweeklydata.xlsx
+++ b/data/historicalweeklydata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frederick Duff\Desktop\Real Estate Project\FORECAST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B961B5D9-C8C3-427B-842F-BD12A4277857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046DE1D7-CE4C-4C00-8B3E-5B5C1A23DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="689" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="689" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Full History" sheetId="3" r:id="rId1"/>
@@ -57,7 +57,7 @@
     <numFmt numFmtId="164" formatCode="0.00_)"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
-  <fonts count="192" x14ac:knownFonts="1">
+  <fonts count="192">
     <font>
       <sz val="12"/>
       <name val="Helv"/>
@@ -2443,14 +2443,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr transitionEvaluation="1"/>
-  <dimension ref="A1:K845"/>
-  <sheetFormatPr defaultColWidth="9.86328125" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:K855"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10.81640625" style="1" customWidth="1" collapsed="1"/>
     <col min="2" max="3" width="11" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.2" thickTop="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:11" ht="15.6" thickTop="1">
       <c r="A2" s="5">
         <v>40179</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:11">
       <c r="A3" s="5">
         <v>40185</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:11">
       <c r="A4" s="5">
         <v>40192</v>
       </c>
@@ -2518,7 +2518,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:11">
       <c r="A5" s="5">
         <v>40199</v>
       </c>
@@ -2537,7 +2537,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:11">
       <c r="A6" s="5">
         <v>40206</v>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:11">
       <c r="A7" s="5">
         <v>40213</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:11">
       <c r="A8" s="5">
         <v>40220</v>
       </c>
@@ -2594,7 +2594,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:11">
       <c r="A9" s="5">
         <v>40227</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:11">
       <c r="A10" s="5">
         <v>40234</v>
       </c>
@@ -2632,7 +2632,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:11">
       <c r="A11" s="5">
         <v>40241</v>
       </c>
@@ -2651,7 +2651,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:11">
       <c r="A12" s="5">
         <v>40248</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:11">
       <c r="A13" s="5">
         <v>40255</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:11">
       <c r="A14" s="5">
         <v>40262</v>
       </c>
@@ -2708,7 +2708,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:11">
       <c r="A15" s="5">
         <v>40269</v>
       </c>
@@ -2727,7 +2727,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:11">
       <c r="A16" s="5">
         <v>40276</v>
       </c>
@@ -2746,7 +2746,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:11">
       <c r="A17" s="5">
         <v>40283</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:11">
       <c r="A18" s="5">
         <v>40290</v>
       </c>
@@ -2784,7 +2784,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:11">
       <c r="A19" s="5">
         <v>40297</v>
       </c>
@@ -2803,7 +2803,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:11">
       <c r="A20" s="5">
         <v>40304</v>
       </c>
@@ -2822,7 +2822,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:11">
       <c r="A21" s="5">
         <v>40311</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:11">
       <c r="A22" s="5">
         <v>40318</v>
       </c>
@@ -2860,7 +2860,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:11">
       <c r="A23" s="5">
         <v>40325</v>
       </c>
@@ -2879,7 +2879,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:11">
       <c r="A24" s="5">
         <v>40332</v>
       </c>
@@ -2898,7 +2898,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:11">
       <c r="A25" s="5">
         <v>40339</v>
       </c>
@@ -2917,7 +2917,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:11">
       <c r="A26" s="5">
         <v>40346</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:11">
       <c r="A27" s="5">
         <v>40353</v>
       </c>
@@ -2955,7 +2955,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:11">
       <c r="A28" s="5">
         <v>40360</v>
       </c>
@@ -2974,7 +2974,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:11">
       <c r="A29" s="5">
         <v>40367</v>
       </c>
@@ -2993,7 +2993,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:11">
       <c r="A30" s="5">
         <v>40374</v>
       </c>
@@ -3012,7 +3012,7 @@
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
     </row>
-    <row r="31" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:11">
       <c r="A31" s="5">
         <v>40381</v>
       </c>
@@ -3031,7 +3031,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:11">
       <c r="A32" s="5">
         <v>40388</v>
       </c>
@@ -3050,7 +3050,7 @@
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:11">
       <c r="A33" s="5">
         <v>40395</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:11">
       <c r="A34" s="5">
         <v>40402</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:11">
       <c r="A35" s="5">
         <v>40409</v>
       </c>
@@ -3107,7 +3107,7 @@
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:11">
       <c r="A36" s="5">
         <v>40416</v>
       </c>
@@ -3126,7 +3126,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:11">
       <c r="A37" s="5">
         <v>40423</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:11">
       <c r="A38" s="5">
         <v>40430</v>
       </c>
@@ -3164,7 +3164,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
     </row>
-    <row r="39" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:11">
       <c r="A39" s="5">
         <v>40437</v>
       </c>
@@ -3183,7 +3183,7 @@
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:11">
       <c r="A40" s="5">
         <v>40444</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
     </row>
-    <row r="41" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:11">
       <c r="A41" s="5">
         <v>40451</v>
       </c>
@@ -3221,7 +3221,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="42" spans="1:11">
       <c r="A42" s="5">
         <v>40458</v>
       </c>
@@ -3240,7 +3240,7 @@
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="43" spans="1:11">
       <c r="A43" s="5">
         <v>40465</v>
       </c>
@@ -3259,7 +3259,7 @@
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:11">
       <c r="A44" s="5">
         <v>40472</v>
       </c>
@@ -3278,7 +3278,7 @@
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
     </row>
-    <row r="45" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="45" spans="1:11">
       <c r="A45" s="5">
         <v>40479</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="46" spans="1:11">
       <c r="A46" s="5">
         <v>40486</v>
       </c>
@@ -3316,7 +3316,7 @@
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="47" spans="1:11">
       <c r="A47" s="5">
         <v>40493</v>
       </c>
@@ -3335,7 +3335,7 @@
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="48" spans="1:11">
       <c r="A48" s="5">
         <v>40500</v>
       </c>
@@ -3354,7 +3354,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="49" spans="1:11">
       <c r="A49" s="5">
         <v>40506</v>
       </c>
@@ -3373,7 +3373,7 @@
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="50" spans="1:11">
       <c r="A50" s="5">
         <v>40514</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="J50" s="7"/>
       <c r="K50" s="7"/>
     </row>
-    <row r="51" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="51" spans="1:11">
       <c r="A51" s="5">
         <v>40521</v>
       </c>
@@ -3411,7 +3411,7 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="52" spans="1:11">
       <c r="A52" s="5">
         <v>40528</v>
       </c>
@@ -3430,7 +3430,7 @@
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
     </row>
-    <row r="53" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="53" spans="1:11">
       <c r="A53" s="5">
         <v>40535</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="54" spans="1:11">
       <c r="A54" s="5">
         <v>40542</v>
       </c>
@@ -3468,7 +3468,7 @@
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
     </row>
-    <row r="55" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="55" spans="1:11">
       <c r="A55" s="5">
         <v>40549</v>
       </c>
@@ -3487,7 +3487,7 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="56" spans="1:11">
       <c r="A56" s="5">
         <v>40556</v>
       </c>
@@ -3506,7 +3506,7 @@
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
     </row>
-    <row r="57" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="57" spans="1:11">
       <c r="A57" s="5">
         <v>40563</v>
       </c>
@@ -3525,7 +3525,7 @@
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="58" spans="1:11">
       <c r="A58" s="5">
         <v>40570</v>
       </c>
@@ -3544,7 +3544,7 @@
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
     </row>
-    <row r="59" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="59" spans="1:11">
       <c r="A59" s="5">
         <v>40577</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
     </row>
-    <row r="60" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="60" spans="1:11">
       <c r="A60" s="5">
         <v>40584</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
     </row>
-    <row r="61" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="61" spans="1:11">
       <c r="A61" s="5">
         <v>40591</v>
       </c>
@@ -3601,7 +3601,7 @@
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
     </row>
-    <row r="62" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="62" spans="1:11">
       <c r="A62" s="5">
         <v>40598</v>
       </c>
@@ -3620,7 +3620,7 @@
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
     </row>
-    <row r="63" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="63" spans="1:11">
       <c r="A63" s="5">
         <v>40605</v>
       </c>
@@ -3639,7 +3639,7 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
     </row>
-    <row r="64" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="64" spans="1:11">
       <c r="A64" s="5">
         <v>40612</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="65" spans="1:11">
       <c r="A65" s="5">
         <v>40619</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="66" spans="1:11">
       <c r="A66" s="5">
         <v>40626</v>
       </c>
@@ -3696,7 +3696,7 @@
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
     </row>
-    <row r="67" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="67" spans="1:11">
       <c r="A67" s="5">
         <v>40633</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="68" spans="1:11">
       <c r="A68" s="5">
         <v>40640</v>
       </c>
@@ -3734,7 +3734,7 @@
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
     </row>
-    <row r="69" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="69" spans="1:11">
       <c r="A69" s="5">
         <v>40647</v>
       </c>
@@ -3753,7 +3753,7 @@
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
     </row>
-    <row r="70" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="70" spans="1:11">
       <c r="A70" s="5">
         <v>40654</v>
       </c>
@@ -3772,7 +3772,7 @@
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
     </row>
-    <row r="71" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="71" spans="1:11">
       <c r="A71" s="5">
         <v>40661</v>
       </c>
@@ -3791,7 +3791,7 @@
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
     </row>
-    <row r="72" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="72" spans="1:11">
       <c r="A72" s="5">
         <v>40668</v>
       </c>
@@ -3810,7 +3810,7 @@
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
     </row>
-    <row r="73" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="73" spans="1:11">
       <c r="A73" s="5">
         <v>40675</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
     </row>
-    <row r="74" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="74" spans="1:11">
       <c r="A74" s="5">
         <v>40682</v>
       </c>
@@ -3848,7 +3848,7 @@
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="75" spans="1:11">
       <c r="A75" s="5">
         <v>40689</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="76" spans="1:11">
       <c r="A76" s="5">
         <v>40696</v>
       </c>
@@ -3886,7 +3886,7 @@
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="77" spans="1:11">
       <c r="A77" s="5">
         <v>40703</v>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
     </row>
-    <row r="78" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="78" spans="1:11">
       <c r="A78" s="5">
         <v>40710</v>
       </c>
@@ -3924,7 +3924,7 @@
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
     </row>
-    <row r="79" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="79" spans="1:11">
       <c r="A79" s="5">
         <v>40717</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="80" spans="1:11">
       <c r="A80" s="5">
         <v>40724</v>
       </c>
@@ -3962,7 +3962,7 @@
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
     </row>
-    <row r="81" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="81" spans="1:11">
       <c r="A81" s="5">
         <v>40731</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
     </row>
-    <row r="82" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="82" spans="1:11">
       <c r="A82" s="5">
         <v>40738</v>
       </c>
@@ -4000,7 +4000,7 @@
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="83" spans="1:11">
       <c r="A83" s="5">
         <v>40745</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
     </row>
-    <row r="84" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="84" spans="1:11">
       <c r="A84" s="5">
         <v>40752</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
     </row>
-    <row r="85" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="85" spans="1:11">
       <c r="A85" s="5">
         <v>40759</v>
       </c>
@@ -4057,7 +4057,7 @@
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
     </row>
-    <row r="86" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="86" spans="1:11">
       <c r="A86" s="5">
         <v>40766</v>
       </c>
@@ -4076,7 +4076,7 @@
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
     </row>
-    <row r="87" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="87" spans="1:11">
       <c r="A87" s="5">
         <v>40773</v>
       </c>
@@ -4095,7 +4095,7 @@
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
     </row>
-    <row r="88" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="88" spans="1:11">
       <c r="A88" s="5">
         <v>40780</v>
       </c>
@@ -4114,7 +4114,7 @@
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
     </row>
-    <row r="89" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="89" spans="1:11">
       <c r="A89" s="5">
         <v>40787</v>
       </c>
@@ -4133,7 +4133,7 @@
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
     </row>
-    <row r="90" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="90" spans="1:11">
       <c r="A90" s="5">
         <v>40794</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
     </row>
-    <row r="91" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="91" spans="1:11">
       <c r="A91" s="5">
         <v>40801</v>
       </c>
@@ -4171,7 +4171,7 @@
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
     </row>
-    <row r="92" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="92" spans="1:11">
       <c r="A92" s="5">
         <v>40808</v>
       </c>
@@ -4190,7 +4190,7 @@
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="93" spans="1:11">
       <c r="A93" s="5">
         <v>40815</v>
       </c>
@@ -4209,7 +4209,7 @@
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
     </row>
-    <row r="94" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="94" spans="1:11">
       <c r="A94" s="5">
         <v>40822</v>
       </c>
@@ -4228,7 +4228,7 @@
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
     </row>
-    <row r="95" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="95" spans="1:11">
       <c r="A95" s="5">
         <v>40829</v>
       </c>
@@ -4247,7 +4247,7 @@
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
     </row>
-    <row r="96" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="96" spans="1:11">
       <c r="A96" s="5">
         <v>40836</v>
       </c>
@@ -4266,7 +4266,7 @@
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
     </row>
-    <row r="97" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="97" spans="1:11">
       <c r="A97" s="5">
         <v>40843</v>
       </c>
@@ -4285,7 +4285,7 @@
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
     </row>
-    <row r="98" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="98" spans="1:11">
       <c r="A98" s="5">
         <v>40850</v>
       </c>
@@ -4304,7 +4304,7 @@
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
     </row>
-    <row r="99" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="99" spans="1:11">
       <c r="A99" s="5">
         <v>40857</v>
       </c>
@@ -4323,7 +4323,7 @@
       <c r="J99" s="7"/>
       <c r="K99" s="7"/>
     </row>
-    <row r="100" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="100" spans="1:11">
       <c r="A100" s="5">
         <v>40864</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
     </row>
-    <row r="101" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="101" spans="1:11">
       <c r="A101" s="5">
         <v>40870</v>
       </c>
@@ -4361,7 +4361,7 @@
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
     </row>
-    <row r="102" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="102" spans="1:11">
       <c r="A102" s="5">
         <v>40878</v>
       </c>
@@ -4380,7 +4380,7 @@
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
     </row>
-    <row r="103" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="103" spans="1:11">
       <c r="A103" s="5">
         <v>40885</v>
       </c>
@@ -4399,7 +4399,7 @@
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
     </row>
-    <row r="104" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="104" spans="1:11">
       <c r="A104" s="5">
         <v>40892</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
     </row>
-    <row r="105" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="105" spans="1:11">
       <c r="A105" s="5">
         <v>40899</v>
       </c>
@@ -4437,7 +4437,7 @@
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
     </row>
-    <row r="106" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="106" spans="1:11">
       <c r="A106" s="5">
         <v>40906</v>
       </c>
@@ -4456,7 +4456,7 @@
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
     </row>
-    <row r="107" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="107" spans="1:11">
       <c r="A107" s="5">
         <v>40913</v>
       </c>
@@ -4475,7 +4475,7 @@
       <c r="J107" s="7"/>
       <c r="K107" s="7"/>
     </row>
-    <row r="108" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="108" spans="1:11">
       <c r="A108" s="5">
         <v>40920</v>
       </c>
@@ -4494,7 +4494,7 @@
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
     </row>
-    <row r="109" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="109" spans="1:11">
       <c r="A109" s="5">
         <v>40927</v>
       </c>
@@ -4513,7 +4513,7 @@
       <c r="J109" s="7"/>
       <c r="K109" s="7"/>
     </row>
-    <row r="110" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="110" spans="1:11">
       <c r="A110" s="5">
         <v>40934</v>
       </c>
@@ -4532,7 +4532,7 @@
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
     </row>
-    <row r="111" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="111" spans="1:11">
       <c r="A111" s="5">
         <v>40941</v>
       </c>
@@ -4551,7 +4551,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
     </row>
-    <row r="112" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="112" spans="1:11">
       <c r="A112" s="5">
         <v>40948</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="7"/>
     </row>
-    <row r="113" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="113" spans="1:11">
       <c r="A113" s="5">
         <v>40955</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
     </row>
-    <row r="114" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="114" spans="1:11">
       <c r="A114" s="5">
         <v>40962</v>
       </c>
@@ -4608,7 +4608,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
     </row>
-    <row r="115" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="115" spans="1:11">
       <c r="A115" s="5">
         <v>40969</v>
       </c>
@@ -4627,7 +4627,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
     </row>
-    <row r="116" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="116" spans="1:11">
       <c r="A116" s="5">
         <v>40976</v>
       </c>
@@ -4646,7 +4646,7 @@
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
     </row>
-    <row r="117" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="117" spans="1:11">
       <c r="A117" s="5">
         <v>40983</v>
       </c>
@@ -4665,7 +4665,7 @@
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
     </row>
-    <row r="118" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="118" spans="1:11">
       <c r="A118" s="5">
         <v>40990</v>
       </c>
@@ -4684,7 +4684,7 @@
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
     </row>
-    <row r="119" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="119" spans="1:11">
       <c r="A119" s="5">
         <v>40997</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="J119" s="7"/>
       <c r="K119" s="7"/>
     </row>
-    <row r="120" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="120" spans="1:11">
       <c r="A120" s="5">
         <v>41004</v>
       </c>
@@ -4722,7 +4722,7 @@
       <c r="J120" s="7"/>
       <c r="K120" s="7"/>
     </row>
-    <row r="121" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="121" spans="1:11">
       <c r="A121" s="5">
         <v>41011</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="J121" s="7"/>
       <c r="K121" s="7"/>
     </row>
-    <row r="122" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="122" spans="1:11">
       <c r="A122" s="5">
         <v>41018</v>
       </c>
@@ -4760,7 +4760,7 @@
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
     </row>
-    <row r="123" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="123" spans="1:11">
       <c r="A123" s="5">
         <v>41025</v>
       </c>
@@ -4779,7 +4779,7 @@
       <c r="J123" s="7"/>
       <c r="K123" s="7"/>
     </row>
-    <row r="124" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="124" spans="1:11">
       <c r="A124" s="5">
         <v>41032</v>
       </c>
@@ -4798,7 +4798,7 @@
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
     </row>
-    <row r="125" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="125" spans="1:11">
       <c r="A125" s="5">
         <v>41039</v>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="J125" s="7"/>
       <c r="K125" s="7"/>
     </row>
-    <row r="126" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="126" spans="1:11">
       <c r="A126" s="5">
         <v>41046</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="J126" s="7"/>
       <c r="K126" s="7"/>
     </row>
-    <row r="127" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="127" spans="1:11">
       <c r="A127" s="5">
         <v>41053</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="J127" s="7"/>
       <c r="K127" s="7"/>
     </row>
-    <row r="128" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="128" spans="1:11">
       <c r="A128" s="5">
         <v>41060</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
     </row>
-    <row r="129" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="129" spans="1:11">
       <c r="A129" s="5">
         <v>41067</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
     </row>
-    <row r="130" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="130" spans="1:11">
       <c r="A130" s="5">
         <v>41074</v>
       </c>
@@ -4912,7 +4912,7 @@
       <c r="J130" s="7"/>
       <c r="K130" s="7"/>
     </row>
-    <row r="131" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="131" spans="1:11">
       <c r="A131" s="5">
         <v>41081</v>
       </c>
@@ -4931,7 +4931,7 @@
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
     </row>
-    <row r="132" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="132" spans="1:11">
       <c r="A132" s="5">
         <v>41088</v>
       </c>
@@ -4950,7 +4950,7 @@
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
     </row>
-    <row r="133" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="133" spans="1:11">
       <c r="A133" s="5">
         <v>41095</v>
       </c>
@@ -4969,7 +4969,7 @@
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
     </row>
-    <row r="134" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="134" spans="1:11">
       <c r="A134" s="5">
         <v>41102</v>
       </c>
@@ -4988,7 +4988,7 @@
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
     </row>
-    <row r="135" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="135" spans="1:11">
       <c r="A135" s="5">
         <v>41109</v>
       </c>
@@ -5007,7 +5007,7 @@
       <c r="J135" s="7"/>
       <c r="K135" s="7"/>
     </row>
-    <row r="136" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="136" spans="1:11">
       <c r="A136" s="5">
         <v>41116</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="J136" s="7"/>
       <c r="K136" s="7"/>
     </row>
-    <row r="137" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="137" spans="1:11">
       <c r="A137" s="5">
         <v>41123</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="J137" s="7"/>
       <c r="K137" s="7"/>
     </row>
-    <row r="138" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="138" spans="1:11">
       <c r="A138" s="5">
         <v>41130</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="J138" s="7"/>
       <c r="K138" s="7"/>
     </row>
-    <row r="139" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="139" spans="1:11">
       <c r="A139" s="5">
         <v>41137</v>
       </c>
@@ -5083,7 +5083,7 @@
       <c r="J139" s="7"/>
       <c r="K139" s="7"/>
     </row>
-    <row r="140" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="140" spans="1:11">
       <c r="A140" s="5">
         <v>41144</v>
       </c>
@@ -5102,7 +5102,7 @@
       <c r="J140" s="7"/>
       <c r="K140" s="7"/>
     </row>
-    <row r="141" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="141" spans="1:11">
       <c r="A141" s="5">
         <v>41151</v>
       </c>
@@ -5121,7 +5121,7 @@
       <c r="J141" s="7"/>
       <c r="K141" s="7"/>
     </row>
-    <row r="142" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="142" spans="1:11">
       <c r="A142" s="5">
         <v>41158</v>
       </c>
@@ -5140,7 +5140,7 @@
       <c r="J142" s="7"/>
       <c r="K142" s="7"/>
     </row>
-    <row r="143" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="143" spans="1:11">
       <c r="A143" s="5">
         <v>41165</v>
       </c>
@@ -5159,7 +5159,7 @@
       <c r="J143" s="7"/>
       <c r="K143" s="7"/>
     </row>
-    <row r="144" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="144" spans="1:11">
       <c r="A144" s="5">
         <v>41172</v>
       </c>
@@ -5178,7 +5178,7 @@
       <c r="J144" s="7"/>
       <c r="K144" s="7"/>
     </row>
-    <row r="145" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="145" spans="1:11">
       <c r="A145" s="5">
         <v>41179</v>
       </c>
@@ -5197,7 +5197,7 @@
       <c r="J145" s="7"/>
       <c r="K145" s="7"/>
     </row>
-    <row r="146" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="146" spans="1:11">
       <c r="A146" s="5">
         <v>41186</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="J146" s="7"/>
       <c r="K146" s="7"/>
     </row>
-    <row r="147" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="147" spans="1:11">
       <c r="A147" s="5">
         <v>41193</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="J147" s="7"/>
       <c r="K147" s="7"/>
     </row>
-    <row r="148" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="148" spans="1:11">
       <c r="A148" s="5">
         <v>41200</v>
       </c>
@@ -5254,7 +5254,7 @@
       <c r="J148" s="7"/>
       <c r="K148" s="7"/>
     </row>
-    <row r="149" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="149" spans="1:11">
       <c r="A149" s="5">
         <v>41207</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="J149" s="7"/>
       <c r="K149" s="7"/>
     </row>
-    <row r="150" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="150" spans="1:11">
       <c r="A150" s="5">
         <v>41214</v>
       </c>
@@ -5292,7 +5292,7 @@
       <c r="J150" s="7"/>
       <c r="K150" s="7"/>
     </row>
-    <row r="151" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="151" spans="1:11">
       <c r="A151" s="5">
         <v>41221</v>
       </c>
@@ -5311,7 +5311,7 @@
       <c r="J151" s="7"/>
       <c r="K151" s="7"/>
     </row>
-    <row r="152" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="152" spans="1:11">
       <c r="A152" s="5">
         <v>41228</v>
       </c>
@@ -5330,7 +5330,7 @@
       <c r="J152" s="7"/>
       <c r="K152" s="7"/>
     </row>
-    <row r="153" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="153" spans="1:11">
       <c r="A153" s="5">
         <v>41234</v>
       </c>
@@ -5349,7 +5349,7 @@
       <c r="J153" s="7"/>
       <c r="K153" s="7"/>
     </row>
-    <row r="154" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="154" spans="1:11">
       <c r="A154" s="5">
         <v>41242</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="J154" s="7"/>
       <c r="K154" s="7"/>
     </row>
-    <row r="155" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="155" spans="1:11">
       <c r="A155" s="5">
         <v>41249</v>
       </c>
@@ -5387,7 +5387,7 @@
       <c r="J155" s="7"/>
       <c r="K155" s="7"/>
     </row>
-    <row r="156" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="156" spans="1:11">
       <c r="A156" s="5">
         <v>41256</v>
       </c>
@@ -5406,7 +5406,7 @@
       <c r="J156" s="7"/>
       <c r="K156" s="7"/>
     </row>
-    <row r="157" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="157" spans="1:11">
       <c r="A157" s="5">
         <v>41263</v>
       </c>
@@ -5425,7 +5425,7 @@
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
     </row>
-    <row r="158" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="158" spans="1:11">
       <c r="A158" s="5">
         <v>41270</v>
       </c>
@@ -5444,7 +5444,7 @@
       <c r="J158" s="7"/>
       <c r="K158" s="7"/>
     </row>
-    <row r="159" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="159" spans="1:11">
       <c r="A159" s="5">
         <v>41277</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="J159" s="7"/>
       <c r="K159" s="7"/>
     </row>
-    <row r="160" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="160" spans="1:11">
       <c r="A160" s="5">
         <v>41284</v>
       </c>
@@ -5482,7 +5482,7 @@
       <c r="J160" s="7"/>
       <c r="K160" s="7"/>
     </row>
-    <row r="161" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="161" spans="1:11">
       <c r="A161" s="5">
         <v>41291</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="J161" s="7"/>
       <c r="K161" s="7"/>
     </row>
-    <row r="162" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="162" spans="1:11">
       <c r="A162" s="5">
         <v>41298</v>
       </c>
@@ -5520,7 +5520,7 @@
       <c r="J162" s="7"/>
       <c r="K162" s="7"/>
     </row>
-    <row r="163" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="163" spans="1:11">
       <c r="A163" s="5">
         <v>41305</v>
       </c>
@@ -5539,7 +5539,7 @@
       <c r="J163" s="7"/>
       <c r="K163" s="7"/>
     </row>
-    <row r="164" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="164" spans="1:11">
       <c r="A164" s="5">
         <v>41312</v>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="J164" s="7"/>
       <c r="K164" s="7"/>
     </row>
-    <row r="165" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="165" spans="1:11">
       <c r="A165" s="5">
         <v>41319</v>
       </c>
@@ -5577,7 +5577,7 @@
       <c r="J165" s="7"/>
       <c r="K165" s="7"/>
     </row>
-    <row r="166" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="166" spans="1:11">
       <c r="A166" s="5">
         <v>41326</v>
       </c>
@@ -5596,7 +5596,7 @@
       <c r="J166" s="7"/>
       <c r="K166" s="7"/>
     </row>
-    <row r="167" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="167" spans="1:11">
       <c r="A167" s="5">
         <v>41333</v>
       </c>
@@ -5615,7 +5615,7 @@
       <c r="J167" s="7"/>
       <c r="K167" s="7"/>
     </row>
-    <row r="168" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="168" spans="1:11">
       <c r="A168" s="5">
         <v>41340</v>
       </c>
@@ -5634,7 +5634,7 @@
       <c r="J168" s="7"/>
       <c r="K168" s="7"/>
     </row>
-    <row r="169" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="169" spans="1:11">
       <c r="A169" s="5">
         <v>41347</v>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="J169" s="7"/>
       <c r="K169" s="7"/>
     </row>
-    <row r="170" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="170" spans="1:11">
       <c r="A170" s="5">
         <v>41354</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="J170" s="7"/>
       <c r="K170" s="7"/>
     </row>
-    <row r="171" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="171" spans="1:11">
       <c r="A171" s="5">
         <v>41361</v>
       </c>
@@ -5691,7 +5691,7 @@
       <c r="J171" s="7"/>
       <c r="K171" s="7"/>
     </row>
-    <row r="172" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="172" spans="1:11">
       <c r="A172" s="5">
         <v>41368</v>
       </c>
@@ -5710,7 +5710,7 @@
       <c r="J172" s="7"/>
       <c r="K172" s="7"/>
     </row>
-    <row r="173" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="173" spans="1:11">
       <c r="A173" s="5">
         <v>41375</v>
       </c>
@@ -5729,7 +5729,7 @@
       <c r="J173" s="7"/>
       <c r="K173" s="7"/>
     </row>
-    <row r="174" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="174" spans="1:11">
       <c r="A174" s="5">
         <v>41382</v>
       </c>
@@ -5748,7 +5748,7 @@
       <c r="J174" s="7"/>
       <c r="K174" s="7"/>
     </row>
-    <row r="175" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="175" spans="1:11">
       <c r="A175" s="5">
         <v>41389</v>
       </c>
@@ -5767,7 +5767,7 @@
       <c r="J175" s="7"/>
       <c r="K175" s="7"/>
     </row>
-    <row r="176" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="176" spans="1:11">
       <c r="A176" s="5">
         <v>41396</v>
       </c>
@@ -5786,7 +5786,7 @@
       <c r="J176" s="7"/>
       <c r="K176" s="7"/>
     </row>
-    <row r="177" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="177" spans="1:11">
       <c r="A177" s="5">
         <v>41403</v>
       </c>
@@ -5805,7 +5805,7 @@
       <c r="J177" s="7"/>
       <c r="K177" s="7"/>
     </row>
-    <row r="178" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="178" spans="1:11">
       <c r="A178" s="5">
         <v>41410</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="J178" s="7"/>
       <c r="K178" s="7"/>
     </row>
-    <row r="179" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="179" spans="1:11">
       <c r="A179" s="5">
         <v>41417</v>
       </c>
@@ -5843,7 +5843,7 @@
       <c r="J179" s="7"/>
       <c r="K179" s="7"/>
     </row>
-    <row r="180" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="180" spans="1:11">
       <c r="A180" s="5">
         <v>41424</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="J180" s="7"/>
       <c r="K180" s="7"/>
     </row>
-    <row r="181" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="181" spans="1:11">
       <c r="A181" s="5">
         <v>41431</v>
       </c>
@@ -5881,7 +5881,7 @@
       <c r="J181" s="7"/>
       <c r="K181" s="7"/>
     </row>
-    <row r="182" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="182" spans="1:11">
       <c r="A182" s="5">
         <v>41438</v>
       </c>
@@ -5900,7 +5900,7 @@
       <c r="J182" s="7"/>
       <c r="K182" s="7"/>
     </row>
-    <row r="183" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="183" spans="1:11">
       <c r="A183" s="5">
         <v>41445</v>
       </c>
@@ -5919,7 +5919,7 @@
       <c r="J183" s="7"/>
       <c r="K183" s="7"/>
     </row>
-    <row r="184" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="184" spans="1:11">
       <c r="A184" s="5">
         <v>41452</v>
       </c>
@@ -5938,7 +5938,7 @@
       <c r="J184" s="7"/>
       <c r="K184" s="7"/>
     </row>
-    <row r="185" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="185" spans="1:11">
       <c r="A185" s="5">
         <v>41458</v>
       </c>
@@ -5957,7 +5957,7 @@
       <c r="J185" s="7"/>
       <c r="K185" s="7"/>
     </row>
-    <row r="186" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="186" spans="1:11">
       <c r="A186" s="5">
         <v>41466</v>
       </c>
@@ -5976,7 +5976,7 @@
       <c r="J186" s="7"/>
       <c r="K186" s="7"/>
     </row>
-    <row r="187" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="187" spans="1:11">
       <c r="A187" s="5">
         <v>41473</v>
       </c>
@@ -5995,7 +5995,7 @@
       <c r="J187" s="7"/>
       <c r="K187" s="7"/>
     </row>
-    <row r="188" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="188" spans="1:11">
       <c r="A188" s="5">
         <v>41480</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="J188" s="7"/>
       <c r="K188" s="7"/>
     </row>
-    <row r="189" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="189" spans="1:11">
       <c r="A189" s="5">
         <v>41487</v>
       </c>
@@ -6033,7 +6033,7 @@
       <c r="J189" s="7"/>
       <c r="K189" s="7"/>
     </row>
-    <row r="190" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="190" spans="1:11">
       <c r="A190" s="5">
         <v>41494</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="J190" s="7"/>
       <c r="K190" s="7"/>
     </row>
-    <row r="191" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="191" spans="1:11">
       <c r="A191" s="5">
         <v>41501</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
     </row>
-    <row r="192" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="192" spans="1:11">
       <c r="A192" s="5">
         <v>41508</v>
       </c>
@@ -6090,7 +6090,7 @@
       <c r="J192" s="7"/>
       <c r="K192" s="7"/>
     </row>
-    <row r="193" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="193" spans="1:11">
       <c r="A193" s="5">
         <v>41515</v>
       </c>
@@ -6109,7 +6109,7 @@
       <c r="J193" s="7"/>
       <c r="K193" s="7"/>
     </row>
-    <row r="194" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="194" spans="1:11">
       <c r="A194" s="5">
         <v>41522</v>
       </c>
@@ -6128,7 +6128,7 @@
       <c r="J194" s="7"/>
       <c r="K194" s="7"/>
     </row>
-    <row r="195" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="195" spans="1:11">
       <c r="A195" s="5">
         <v>41529</v>
       </c>
@@ -6147,7 +6147,7 @@
       <c r="J195" s="7"/>
       <c r="K195" s="7"/>
     </row>
-    <row r="196" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="196" spans="1:11">
       <c r="A196" s="5">
         <v>41536</v>
       </c>
@@ -6166,7 +6166,7 @@
       <c r="J196" s="7"/>
       <c r="K196" s="7"/>
     </row>
-    <row r="197" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="197" spans="1:11">
       <c r="A197" s="5">
         <v>41543</v>
       </c>
@@ -6185,7 +6185,7 @@
       <c r="J197" s="7"/>
       <c r="K197" s="7"/>
     </row>
-    <row r="198" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="198" spans="1:11">
       <c r="A198" s="5">
         <v>41550</v>
       </c>
@@ -6204,7 +6204,7 @@
       <c r="J198" s="7"/>
       <c r="K198" s="7"/>
     </row>
-    <row r="199" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="199" spans="1:11">
       <c r="A199" s="5">
         <v>41557</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="J199" s="7"/>
       <c r="K199" s="7"/>
     </row>
-    <row r="200" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="200" spans="1:11">
       <c r="A200" s="5">
         <v>41564</v>
       </c>
@@ -6242,7 +6242,7 @@
       <c r="J200" s="7"/>
       <c r="K200" s="7"/>
     </row>
-    <row r="201" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="201" spans="1:11">
       <c r="A201" s="5">
         <v>41571</v>
       </c>
@@ -6261,7 +6261,7 @@
       <c r="J201" s="7"/>
       <c r="K201" s="7"/>
     </row>
-    <row r="202" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="202" spans="1:11">
       <c r="A202" s="5">
         <v>41578</v>
       </c>
@@ -6280,7 +6280,7 @@
       <c r="J202" s="7"/>
       <c r="K202" s="7"/>
     </row>
-    <row r="203" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="203" spans="1:11">
       <c r="A203" s="5">
         <v>41585</v>
       </c>
@@ -6299,7 +6299,7 @@
       <c r="J203" s="7"/>
       <c r="K203" s="7"/>
     </row>
-    <row r="204" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="204" spans="1:11">
       <c r="A204" s="5">
         <v>41592</v>
       </c>
@@ -6318,7 +6318,7 @@
       <c r="J204" s="7"/>
       <c r="K204" s="7"/>
     </row>
-    <row r="205" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="205" spans="1:11">
       <c r="A205" s="5">
         <v>41599</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="J205" s="7"/>
       <c r="K205" s="7"/>
     </row>
-    <row r="206" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="206" spans="1:11">
       <c r="A206" s="5">
         <v>41605</v>
       </c>
@@ -6356,7 +6356,7 @@
       <c r="J206" s="7"/>
       <c r="K206" s="7"/>
     </row>
-    <row r="207" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="207" spans="1:11">
       <c r="A207" s="5">
         <v>41613</v>
       </c>
@@ -6375,7 +6375,7 @@
       <c r="J207" s="7"/>
       <c r="K207" s="7"/>
     </row>
-    <row r="208" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="208" spans="1:11">
       <c r="A208" s="5">
         <v>41620</v>
       </c>
@@ -6394,7 +6394,7 @@
       <c r="J208" s="7"/>
       <c r="K208" s="7"/>
     </row>
-    <row r="209" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="209" spans="1:11">
       <c r="A209" s="5">
         <v>41627</v>
       </c>
@@ -6413,7 +6413,7 @@
       <c r="J209" s="7"/>
       <c r="K209" s="7"/>
     </row>
-    <row r="210" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="210" spans="1:11">
       <c r="A210" s="5">
         <v>41634</v>
       </c>
@@ -6432,7 +6432,7 @@
       <c r="J210" s="7"/>
       <c r="K210" s="7"/>
     </row>
-    <row r="211" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="211" spans="1:11">
       <c r="A211" s="5">
         <v>41641</v>
       </c>
@@ -6451,7 +6451,7 @@
       <c r="J211" s="7"/>
       <c r="K211" s="7"/>
     </row>
-    <row r="212" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="212" spans="1:11">
       <c r="A212" s="5">
         <v>41648</v>
       </c>
@@ -6470,7 +6470,7 @@
       <c r="J212" s="7"/>
       <c r="K212" s="7"/>
     </row>
-    <row r="213" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="213" spans="1:11">
       <c r="A213" s="5">
         <v>41655</v>
       </c>
@@ -6489,7 +6489,7 @@
       <c r="J213" s="7"/>
       <c r="K213" s="7"/>
     </row>
-    <row r="214" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="214" spans="1:11">
       <c r="A214" s="5">
         <v>41662</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="J214" s="7"/>
       <c r="K214" s="7"/>
     </row>
-    <row r="215" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="215" spans="1:11">
       <c r="A215" s="5">
         <v>41669</v>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="J215" s="7"/>
       <c r="K215" s="7"/>
     </row>
-    <row r="216" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="216" spans="1:11">
       <c r="A216" s="5">
         <v>41676</v>
       </c>
@@ -6546,7 +6546,7 @@
       <c r="J216" s="7"/>
       <c r="K216" s="7"/>
     </row>
-    <row r="217" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="217" spans="1:11">
       <c r="A217" s="5">
         <v>41683</v>
       </c>
@@ -6565,7 +6565,7 @@
       <c r="J217" s="7"/>
       <c r="K217" s="7"/>
     </row>
-    <row r="218" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="218" spans="1:11">
       <c r="A218" s="5">
         <v>41690</v>
       </c>
@@ -6584,7 +6584,7 @@
       <c r="J218" s="7"/>
       <c r="K218" s="7"/>
     </row>
-    <row r="219" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="219" spans="1:11">
       <c r="A219" s="5">
         <v>41697</v>
       </c>
@@ -6603,7 +6603,7 @@
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
     </row>
-    <row r="220" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="220" spans="1:11">
       <c r="A220" s="5">
         <v>41704</v>
       </c>
@@ -6622,7 +6622,7 @@
       <c r="J220" s="7"/>
       <c r="K220" s="7"/>
     </row>
-    <row r="221" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="221" spans="1:11">
       <c r="A221" s="5">
         <v>41711</v>
       </c>
@@ -6641,7 +6641,7 @@
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
     </row>
-    <row r="222" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="222" spans="1:11">
       <c r="A222" s="5">
         <v>41718</v>
       </c>
@@ -6660,7 +6660,7 @@
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
     </row>
-    <row r="223" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="223" spans="1:11">
       <c r="A223" s="5">
         <v>41725</v>
       </c>
@@ -6679,7 +6679,7 @@
       <c r="J223" s="7"/>
       <c r="K223" s="7"/>
     </row>
-    <row r="224" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="224" spans="1:11">
       <c r="A224" s="5">
         <v>41732</v>
       </c>
@@ -6698,7 +6698,7 @@
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
     </row>
-    <row r="225" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="225" spans="1:11">
       <c r="A225" s="5">
         <v>41739</v>
       </c>
@@ -6717,7 +6717,7 @@
       <c r="J225" s="7"/>
       <c r="K225" s="7"/>
     </row>
-    <row r="226" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="226" spans="1:11">
       <c r="A226" s="5">
         <v>41746</v>
       </c>
@@ -6736,7 +6736,7 @@
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
     </row>
-    <row r="227" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="227" spans="1:11">
       <c r="A227" s="5">
         <v>41753</v>
       </c>
@@ -6755,7 +6755,7 @@
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
     </row>
-    <row r="228" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="228" spans="1:11">
       <c r="A228" s="5">
         <v>41760</v>
       </c>
@@ -6774,7 +6774,7 @@
       <c r="J228" s="7"/>
       <c r="K228" s="7"/>
     </row>
-    <row r="229" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="229" spans="1:11">
       <c r="A229" s="5">
         <v>41767</v>
       </c>
@@ -6793,7 +6793,7 @@
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
     </row>
-    <row r="230" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="230" spans="1:11">
       <c r="A230" s="5">
         <v>41774</v>
       </c>
@@ -6812,7 +6812,7 @@
       <c r="J230" s="7"/>
       <c r="K230" s="7"/>
     </row>
-    <row r="231" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="231" spans="1:11">
       <c r="A231" s="5">
         <v>41781</v>
       </c>
@@ -6831,7 +6831,7 @@
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
     </row>
-    <row r="232" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="232" spans="1:11">
       <c r="A232" s="5">
         <v>41788</v>
       </c>
@@ -6850,7 +6850,7 @@
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
     </row>
-    <row r="233" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="233" spans="1:11">
       <c r="A233" s="5">
         <v>41795</v>
       </c>
@@ -6869,7 +6869,7 @@
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
     </row>
-    <row r="234" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="234" spans="1:11">
       <c r="A234" s="5">
         <v>41802</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
     </row>
-    <row r="235" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="235" spans="1:11">
       <c r="A235" s="5">
         <v>41809</v>
       </c>
@@ -6907,7 +6907,7 @@
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
     </row>
-    <row r="236" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="236" spans="1:11">
       <c r="A236" s="5">
         <v>41816</v>
       </c>
@@ -6926,7 +6926,7 @@
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
     </row>
-    <row r="237" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="237" spans="1:11">
       <c r="A237" s="5">
         <v>41823</v>
       </c>
@@ -6945,7 +6945,7 @@
       <c r="J237" s="7"/>
       <c r="K237" s="7"/>
     </row>
-    <row r="238" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="238" spans="1:11">
       <c r="A238" s="5">
         <v>41830</v>
       </c>
@@ -6964,7 +6964,7 @@
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
     </row>
-    <row r="239" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="239" spans="1:11">
       <c r="A239" s="5">
         <v>41837</v>
       </c>
@@ -6983,7 +6983,7 @@
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
     </row>
-    <row r="240" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="240" spans="1:11">
       <c r="A240" s="5">
         <v>41844</v>
       </c>
@@ -7002,7 +7002,7 @@
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
     </row>
-    <row r="241" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="241" spans="1:11">
       <c r="A241" s="5">
         <v>41851</v>
       </c>
@@ -7021,7 +7021,7 @@
       <c r="J241" s="7"/>
       <c r="K241" s="7"/>
     </row>
-    <row r="242" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="242" spans="1:11">
       <c r="A242" s="5">
         <v>41858</v>
       </c>
@@ -7040,7 +7040,7 @@
       <c r="J242" s="7"/>
       <c r="K242" s="7"/>
     </row>
-    <row r="243" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="243" spans="1:11">
       <c r="A243" s="5">
         <v>41865</v>
       </c>
@@ -7059,7 +7059,7 @@
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
     </row>
-    <row r="244" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="244" spans="1:11">
       <c r="A244" s="5">
         <v>41872</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="J244" s="7"/>
       <c r="K244" s="7"/>
     </row>
-    <row r="245" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="245" spans="1:11">
       <c r="A245" s="5">
         <v>41879</v>
       </c>
@@ -7097,7 +7097,7 @@
       <c r="J245" s="7"/>
       <c r="K245" s="7"/>
     </row>
-    <row r="246" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="246" spans="1:11">
       <c r="A246" s="5">
         <v>41886</v>
       </c>
@@ -7116,7 +7116,7 @@
       <c r="J246" s="7"/>
       <c r="K246" s="7"/>
     </row>
-    <row r="247" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="247" spans="1:11">
       <c r="A247" s="5">
         <v>41893</v>
       </c>
@@ -7135,7 +7135,7 @@
       <c r="J247" s="7"/>
       <c r="K247" s="7"/>
     </row>
-    <row r="248" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="248" spans="1:11">
       <c r="A248" s="5">
         <v>41900</v>
       </c>
@@ -7154,7 +7154,7 @@
       <c r="J248" s="7"/>
       <c r="K248" s="7"/>
     </row>
-    <row r="249" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="249" spans="1:11">
       <c r="A249" s="5">
         <v>41907</v>
       </c>
@@ -7173,7 +7173,7 @@
       <c r="J249" s="7"/>
       <c r="K249" s="7"/>
     </row>
-    <row r="250" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="250" spans="1:11">
       <c r="A250" s="5">
         <v>41914</v>
       </c>
@@ -7192,7 +7192,7 @@
       <c r="J250" s="7"/>
       <c r="K250" s="7"/>
     </row>
-    <row r="251" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="251" spans="1:11">
       <c r="A251" s="5">
         <v>41921</v>
       </c>
@@ -7211,7 +7211,7 @@
       <c r="J251" s="7"/>
       <c r="K251" s="7"/>
     </row>
-    <row r="252" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="252" spans="1:11">
       <c r="A252" s="5">
         <v>41928</v>
       </c>
@@ -7230,7 +7230,7 @@
       <c r="J252" s="7"/>
       <c r="K252" s="7"/>
     </row>
-    <row r="253" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="253" spans="1:11">
       <c r="A253" s="5">
         <v>41935</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="J253" s="7"/>
       <c r="K253" s="7"/>
     </row>
-    <row r="254" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="254" spans="1:11">
       <c r="A254" s="5">
         <v>41942</v>
       </c>
@@ -7268,7 +7268,7 @@
       <c r="J254" s="7"/>
       <c r="K254" s="7"/>
     </row>
-    <row r="255" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="255" spans="1:11">
       <c r="A255" s="5">
         <v>41949</v>
       </c>
@@ -7287,7 +7287,7 @@
       <c r="J255" s="7"/>
       <c r="K255" s="7"/>
     </row>
-    <row r="256" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="256" spans="1:11">
       <c r="A256" s="5">
         <v>41956</v>
       </c>
@@ -7306,7 +7306,7 @@
       <c r="J256" s="7"/>
       <c r="K256" s="7"/>
     </row>
-    <row r="257" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="257" spans="1:11">
       <c r="A257" s="5">
         <v>41963</v>
       </c>
@@ -7325,7 +7325,7 @@
       <c r="J257" s="7"/>
       <c r="K257" s="7"/>
     </row>
-    <row r="258" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="258" spans="1:11">
       <c r="A258" s="5">
         <v>41969</v>
       </c>
@@ -7344,7 +7344,7 @@
       <c r="J258" s="7"/>
       <c r="K258" s="7"/>
     </row>
-    <row r="259" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="259" spans="1:11">
       <c r="A259" s="5">
         <v>41977</v>
       </c>
@@ -7363,7 +7363,7 @@
       <c r="J259" s="7"/>
       <c r="K259" s="7"/>
     </row>
-    <row r="260" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="260" spans="1:11">
       <c r="A260" s="5">
         <v>41984</v>
       </c>
@@ -7382,7 +7382,7 @@
       <c r="J260" s="7"/>
       <c r="K260" s="7"/>
     </row>
-    <row r="261" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="261" spans="1:11">
       <c r="A261" s="5">
         <v>41991</v>
       </c>
@@ -7401,7 +7401,7 @@
       <c r="J261" s="7"/>
       <c r="K261" s="7"/>
     </row>
-    <row r="262" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="262" spans="1:11">
       <c r="A262" s="5">
         <v>41997</v>
       </c>
@@ -7420,7 +7420,7 @@
       <c r="J262" s="7"/>
       <c r="K262" s="7"/>
     </row>
-    <row r="263" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="263" spans="1:11">
       <c r="A263" s="5">
         <v>42004</v>
       </c>
@@ -7439,7 +7439,7 @@
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
     </row>
-    <row r="264" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="264" spans="1:11">
       <c r="A264" s="5">
         <v>42012</v>
       </c>
@@ -7458,7 +7458,7 @@
       <c r="J264" s="7"/>
       <c r="K264" s="7"/>
     </row>
-    <row r="265" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="265" spans="1:11">
       <c r="A265" s="5">
         <v>42019</v>
       </c>
@@ -7477,7 +7477,7 @@
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
     </row>
-    <row r="266" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="266" spans="1:11">
       <c r="A266" s="5">
         <v>42026</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
     </row>
-    <row r="267" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="267" spans="1:11">
       <c r="A267" s="5">
         <v>42033</v>
       </c>
@@ -7515,7 +7515,7 @@
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
     </row>
-    <row r="268" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="268" spans="1:11">
       <c r="A268" s="5">
         <v>42040</v>
       </c>
@@ -7534,7 +7534,7 @@
       <c r="J268" s="7"/>
       <c r="K268" s="7"/>
     </row>
-    <row r="269" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="269" spans="1:11">
       <c r="A269" s="5">
         <v>42047</v>
       </c>
@@ -7553,7 +7553,7 @@
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
     </row>
-    <row r="270" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="270" spans="1:11">
       <c r="A270" s="5">
         <v>42054</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
     </row>
-    <row r="271" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="271" spans="1:11">
       <c r="A271" s="5">
         <v>42061</v>
       </c>
@@ -7591,7 +7591,7 @@
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
     </row>
-    <row r="272" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="272" spans="1:11">
       <c r="A272" s="5">
         <v>42068</v>
       </c>
@@ -7610,7 +7610,7 @@
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
     </row>
-    <row r="273" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="273" spans="1:11">
       <c r="A273" s="5">
         <v>42075</v>
       </c>
@@ -7629,7 +7629,7 @@
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
     </row>
-    <row r="274" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="274" spans="1:11">
       <c r="A274" s="5">
         <v>42082</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
     </row>
-    <row r="275" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="275" spans="1:11">
       <c r="A275" s="5">
         <v>42089</v>
       </c>
@@ -7667,7 +7667,7 @@
       <c r="J275" s="7"/>
       <c r="K275" s="7"/>
     </row>
-    <row r="276" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="276" spans="1:11">
       <c r="A276" s="5">
         <v>42096</v>
       </c>
@@ -7686,7 +7686,7 @@
       <c r="J276" s="7"/>
       <c r="K276" s="7"/>
     </row>
-    <row r="277" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="277" spans="1:11">
       <c r="A277" s="5">
         <v>42103</v>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="J277" s="7"/>
       <c r="K277" s="7"/>
     </row>
-    <row r="278" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="278" spans="1:11">
       <c r="A278" s="5">
         <v>42110</v>
       </c>
@@ -7724,7 +7724,7 @@
       <c r="J278" s="7"/>
       <c r="K278" s="7"/>
     </row>
-    <row r="279" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="279" spans="1:11">
       <c r="A279" s="5">
         <v>42117</v>
       </c>
@@ -7743,7 +7743,7 @@
       <c r="J279" s="7"/>
       <c r="K279" s="7"/>
     </row>
-    <row r="280" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="280" spans="1:11">
       <c r="A280" s="5">
         <v>42124</v>
       </c>
@@ -7762,7 +7762,7 @@
       <c r="J280" s="7"/>
       <c r="K280" s="7"/>
     </row>
-    <row r="281" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="281" spans="1:11">
       <c r="A281" s="5">
         <v>42131</v>
       </c>
@@ -7781,7 +7781,7 @@
       <c r="J281" s="7"/>
       <c r="K281" s="7"/>
     </row>
-    <row r="282" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="282" spans="1:11">
       <c r="A282" s="5">
         <v>42138</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="J282" s="7"/>
       <c r="K282" s="7"/>
     </row>
-    <row r="283" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="283" spans="1:11">
       <c r="A283" s="5">
         <v>42145</v>
       </c>
@@ -7819,7 +7819,7 @@
       <c r="J283" s="7"/>
       <c r="K283" s="7"/>
     </row>
-    <row r="284" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="284" spans="1:11">
       <c r="A284" s="5">
         <v>42152</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="J284" s="7"/>
       <c r="K284" s="7"/>
     </row>
-    <row r="285" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="285" spans="1:11">
       <c r="A285" s="5">
         <v>42159</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="J285" s="7"/>
       <c r="K285" s="7"/>
     </row>
-    <row r="286" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="286" spans="1:11">
       <c r="A286" s="5">
         <v>42166</v>
       </c>
@@ -7876,7 +7876,7 @@
       <c r="J286" s="7"/>
       <c r="K286" s="7"/>
     </row>
-    <row r="287" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="287" spans="1:11">
       <c r="A287" s="5">
         <v>42173</v>
       </c>
@@ -7895,7 +7895,7 @@
       <c r="J287" s="7"/>
       <c r="K287" s="7"/>
     </row>
-    <row r="288" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="288" spans="1:11">
       <c r="A288" s="5">
         <v>42180</v>
       </c>
@@ -7914,7 +7914,7 @@
       <c r="J288" s="7"/>
       <c r="K288" s="7"/>
     </row>
-    <row r="289" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="289" spans="1:11">
       <c r="A289" s="5">
         <v>42187</v>
       </c>
@@ -7933,7 +7933,7 @@
       <c r="J289" s="7"/>
       <c r="K289" s="7"/>
     </row>
-    <row r="290" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="290" spans="1:11">
       <c r="A290" s="5">
         <v>42194</v>
       </c>
@@ -7952,7 +7952,7 @@
       <c r="J290" s="7"/>
       <c r="K290" s="7"/>
     </row>
-    <row r="291" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="291" spans="1:11">
       <c r="A291" s="5">
         <v>42201</v>
       </c>
@@ -7971,7 +7971,7 @@
       <c r="J291" s="7"/>
       <c r="K291" s="7"/>
     </row>
-    <row r="292" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="292" spans="1:11">
       <c r="A292" s="5">
         <v>42208</v>
       </c>
@@ -7990,7 +7990,7 @@
       <c r="J292" s="7"/>
       <c r="K292" s="7"/>
     </row>
-    <row r="293" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="293" spans="1:11">
       <c r="A293" s="5">
         <v>42215</v>
       </c>
@@ -8009,7 +8009,7 @@
       <c r="J293" s="7"/>
       <c r="K293" s="7"/>
     </row>
-    <row r="294" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="294" spans="1:11">
       <c r="A294" s="5">
         <v>42222</v>
       </c>
@@ -8028,7 +8028,7 @@
       <c r="J294" s="7"/>
       <c r="K294" s="7"/>
     </row>
-    <row r="295" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="295" spans="1:11">
       <c r="A295" s="5">
         <v>42229</v>
       </c>
@@ -8047,7 +8047,7 @@
       <c r="J295" s="7"/>
       <c r="K295" s="7"/>
     </row>
-    <row r="296" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="296" spans="1:11">
       <c r="A296" s="5">
         <v>42236</v>
       </c>
@@ -8066,7 +8066,7 @@
       <c r="J296" s="7"/>
       <c r="K296" s="7"/>
     </row>
-    <row r="297" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="297" spans="1:11">
       <c r="A297" s="5">
         <v>42243</v>
       </c>
@@ -8085,7 +8085,7 @@
       <c r="J297" s="7"/>
       <c r="K297" s="7"/>
     </row>
-    <row r="298" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="298" spans="1:11">
       <c r="A298" s="5">
         <v>42250</v>
       </c>
@@ -8104,7 +8104,7 @@
       <c r="J298" s="7"/>
       <c r="K298" s="7"/>
     </row>
-    <row r="299" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="299" spans="1:11">
       <c r="A299" s="5">
         <v>42257</v>
       </c>
@@ -8123,7 +8123,7 @@
       <c r="J299" s="7"/>
       <c r="K299" s="7"/>
     </row>
-    <row r="300" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="300" spans="1:11">
       <c r="A300" s="5">
         <v>42264</v>
       </c>
@@ -8142,7 +8142,7 @@
       <c r="J300" s="7"/>
       <c r="K300" s="7"/>
     </row>
-    <row r="301" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="301" spans="1:11">
       <c r="A301" s="5">
         <v>42271</v>
       </c>
@@ -8161,7 +8161,7 @@
       <c r="J301" s="7"/>
       <c r="K301" s="7"/>
     </row>
-    <row r="302" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="302" spans="1:11">
       <c r="A302" s="5">
         <v>42278</v>
       </c>
@@ -8180,7 +8180,7 @@
       <c r="J302" s="7"/>
       <c r="K302" s="7"/>
     </row>
-    <row r="303" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="303" spans="1:11">
       <c r="A303" s="5">
         <v>42285</v>
       </c>
@@ -8199,7 +8199,7 @@
       <c r="J303" s="7"/>
       <c r="K303" s="7"/>
     </row>
-    <row r="304" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="304" spans="1:11">
       <c r="A304" s="5">
         <v>42292</v>
       </c>
@@ -8218,7 +8218,7 @@
       <c r="J304" s="7"/>
       <c r="K304" s="7"/>
     </row>
-    <row r="305" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="305" spans="1:11">
       <c r="A305" s="5">
         <v>42299</v>
       </c>
@@ -8237,7 +8237,7 @@
       <c r="J305" s="7"/>
       <c r="K305" s="7"/>
     </row>
-    <row r="306" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="306" spans="1:11">
       <c r="A306" s="5">
         <v>42306</v>
       </c>
@@ -8256,7 +8256,7 @@
       <c r="J306" s="7"/>
       <c r="K306" s="7"/>
     </row>
-    <row r="307" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="307" spans="1:11">
       <c r="A307" s="5">
         <v>42313</v>
       </c>
@@ -8275,7 +8275,7 @@
       <c r="J307" s="7"/>
       <c r="K307" s="7"/>
     </row>
-    <row r="308" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="308" spans="1:11">
       <c r="A308" s="5">
         <v>42320</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="J308" s="7"/>
       <c r="K308" s="7"/>
     </row>
-    <row r="309" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="309" spans="1:11">
       <c r="A309" s="5">
         <v>42327</v>
       </c>
@@ -8313,7 +8313,7 @@
       <c r="J309" s="7"/>
       <c r="K309" s="7"/>
     </row>
-    <row r="310" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="310" spans="1:11">
       <c r="A310" s="5">
         <v>42333</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="J310" s="7"/>
       <c r="K310" s="7"/>
     </row>
-    <row r="311" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="311" spans="1:11">
       <c r="A311" s="5">
         <v>42341</v>
       </c>
@@ -8351,7 +8351,7 @@
       <c r="J311" s="7"/>
       <c r="K311" s="7"/>
     </row>
-    <row r="312" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="312" spans="1:11">
       <c r="A312" s="5">
         <v>42348</v>
       </c>
@@ -8370,7 +8370,7 @@
       <c r="J312" s="7"/>
       <c r="K312" s="7"/>
     </row>
-    <row r="313" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="313" spans="1:11">
       <c r="A313" s="5">
         <v>42355</v>
       </c>
@@ -8389,7 +8389,7 @@
       <c r="J313" s="7"/>
       <c r="K313" s="7"/>
     </row>
-    <row r="314" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="314" spans="1:11">
       <c r="A314" s="5">
         <v>42362</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="J314" s="7"/>
       <c r="K314" s="7"/>
     </row>
-    <row r="315" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="315" spans="1:11">
       <c r="A315" s="5">
         <v>42369</v>
       </c>
@@ -8427,7 +8427,7 @@
       <c r="J315" s="7"/>
       <c r="K315" s="7"/>
     </row>
-    <row r="316" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="316" spans="1:11">
       <c r="A316" s="5">
         <v>42376</v>
       </c>
@@ -8446,7 +8446,7 @@
       <c r="J316" s="7"/>
       <c r="K316" s="7"/>
     </row>
-    <row r="317" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="317" spans="1:11">
       <c r="A317" s="5">
         <v>42383</v>
       </c>
@@ -8465,7 +8465,7 @@
       <c r="J317" s="7"/>
       <c r="K317" s="7"/>
     </row>
-    <row r="318" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="318" spans="1:11">
       <c r="A318" s="5">
         <v>42390</v>
       </c>
@@ -8484,7 +8484,7 @@
       <c r="J318" s="7"/>
       <c r="K318" s="7"/>
     </row>
-    <row r="319" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="319" spans="1:11">
       <c r="A319" s="5">
         <v>42397</v>
       </c>
@@ -8503,7 +8503,7 @@
       <c r="J319" s="7"/>
       <c r="K319" s="7"/>
     </row>
-    <row r="320" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="320" spans="1:11">
       <c r="A320" s="5">
         <v>42404</v>
       </c>
@@ -8522,7 +8522,7 @@
       <c r="J320" s="7"/>
       <c r="K320" s="7"/>
     </row>
-    <row r="321" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="321" spans="1:11">
       <c r="A321" s="5">
         <v>42411</v>
       </c>
@@ -8541,7 +8541,7 @@
       <c r="J321" s="7"/>
       <c r="K321" s="7"/>
     </row>
-    <row r="322" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="322" spans="1:11">
       <c r="A322" s="5">
         <v>42418</v>
       </c>
@@ -8560,7 +8560,7 @@
       <c r="J322" s="7"/>
       <c r="K322" s="7"/>
     </row>
-    <row r="323" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="323" spans="1:11">
       <c r="A323" s="5">
         <v>42425</v>
       </c>
@@ -8579,7 +8579,7 @@
       <c r="J323" s="7"/>
       <c r="K323" s="7"/>
     </row>
-    <row r="324" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="324" spans="1:11">
       <c r="A324" s="5">
         <v>42432</v>
       </c>
@@ -8598,7 +8598,7 @@
       <c r="J324" s="7"/>
       <c r="K324" s="7"/>
     </row>
-    <row r="325" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="325" spans="1:11">
       <c r="A325" s="5">
         <v>42439</v>
       </c>
@@ -8617,7 +8617,7 @@
       <c r="J325" s="7"/>
       <c r="K325" s="7"/>
     </row>
-    <row r="326" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="326" spans="1:11">
       <c r="A326" s="5">
         <v>42446</v>
       </c>
@@ -8636,7 +8636,7 @@
       <c r="J326" s="7"/>
       <c r="K326" s="7"/>
     </row>
-    <row r="327" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="327" spans="1:11">
       <c r="A327" s="5">
         <v>42453</v>
       </c>
@@ -8655,7 +8655,7 @@
       <c r="J327" s="7"/>
       <c r="K327" s="7"/>
     </row>
-    <row r="328" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="328" spans="1:11">
       <c r="A328" s="5">
         <v>42460</v>
       </c>
@@ -8674,7 +8674,7 @@
       <c r="J328" s="7"/>
       <c r="K328" s="7"/>
     </row>
-    <row r="329" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="329" spans="1:11">
       <c r="A329" s="5">
         <v>42467</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="J329" s="7"/>
       <c r="K329" s="7"/>
     </row>
-    <row r="330" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="330" spans="1:11">
       <c r="A330" s="5">
         <v>42474</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="J330" s="7"/>
       <c r="K330" s="7"/>
     </row>
-    <row r="331" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="331" spans="1:11">
       <c r="A331" s="5">
         <v>42481</v>
       </c>
@@ -8731,7 +8731,7 @@
       <c r="J331" s="7"/>
       <c r="K331" s="7"/>
     </row>
-    <row r="332" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="332" spans="1:11">
       <c r="A332" s="5">
         <v>42488</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="J332" s="7"/>
       <c r="K332" s="7"/>
     </row>
-    <row r="333" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="333" spans="1:11">
       <c r="A333" s="5">
         <v>42495</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="J333" s="7"/>
       <c r="K333" s="7"/>
     </row>
-    <row r="334" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="334" spans="1:11">
       <c r="A334" s="5">
         <v>42502</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="J334" s="7"/>
       <c r="K334" s="7"/>
     </row>
-    <row r="335" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="335" spans="1:11">
       <c r="A335" s="5">
         <v>42509</v>
       </c>
@@ -8807,7 +8807,7 @@
       <c r="J335" s="7"/>
       <c r="K335" s="7"/>
     </row>
-    <row r="336" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="336" spans="1:11">
       <c r="A336" s="5">
         <v>42516</v>
       </c>
@@ -8826,7 +8826,7 @@
       <c r="J336" s="7"/>
       <c r="K336" s="7"/>
     </row>
-    <row r="337" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="337" spans="1:11">
       <c r="A337" s="5">
         <v>42523</v>
       </c>
@@ -8845,7 +8845,7 @@
       <c r="J337" s="7"/>
       <c r="K337" s="7"/>
     </row>
-    <row r="338" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="338" spans="1:11">
       <c r="A338" s="5">
         <v>42530</v>
       </c>
@@ -8864,7 +8864,7 @@
       <c r="J338" s="7"/>
       <c r="K338" s="7"/>
     </row>
-    <row r="339" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="339" spans="1:11">
       <c r="A339" s="5">
         <v>42537</v>
       </c>
@@ -8883,7 +8883,7 @@
       <c r="J339" s="7"/>
       <c r="K339" s="7"/>
     </row>
-    <row r="340" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="340" spans="1:11">
       <c r="A340" s="5">
         <v>42544</v>
       </c>
@@ -8902,7 +8902,7 @@
       <c r="J340" s="7"/>
       <c r="K340" s="7"/>
     </row>
-    <row r="341" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="341" spans="1:11">
       <c r="A341" s="5">
         <v>42551</v>
       </c>
@@ -8921,7 +8921,7 @@
       <c r="J341" s="7"/>
       <c r="K341" s="7"/>
     </row>
-    <row r="342" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="342" spans="1:11">
       <c r="A342" s="5">
         <v>42558</v>
       </c>
@@ -8940,7 +8940,7 @@
       <c r="J342" s="7"/>
       <c r="K342" s="7"/>
     </row>
-    <row r="343" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="343" spans="1:11">
       <c r="A343" s="5">
         <v>42565</v>
       </c>
@@ -8959,7 +8959,7 @@
       <c r="J343" s="7"/>
       <c r="K343" s="7"/>
     </row>
-    <row r="344" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="344" spans="1:11">
       <c r="A344" s="5">
         <v>42572</v>
       </c>
@@ -8978,7 +8978,7 @@
       <c r="J344" s="7"/>
       <c r="K344" s="7"/>
     </row>
-    <row r="345" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="345" spans="1:11">
       <c r="A345" s="5">
         <v>42579</v>
       </c>
@@ -8997,7 +8997,7 @@
       <c r="J345" s="7"/>
       <c r="K345" s="7"/>
     </row>
-    <row r="346" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="346" spans="1:11">
       <c r="A346" s="5">
         <v>42586</v>
       </c>
@@ -9016,7 +9016,7 @@
       <c r="J346" s="7"/>
       <c r="K346" s="7"/>
     </row>
-    <row r="347" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="347" spans="1:11">
       <c r="A347" s="5">
         <v>42593</v>
       </c>
@@ -9035,7 +9035,7 @@
       <c r="J347" s="7"/>
       <c r="K347" s="7"/>
     </row>
-    <row r="348" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="348" spans="1:11">
       <c r="A348" s="5">
         <v>42600</v>
       </c>
@@ -9054,7 +9054,7 @@
       <c r="J348" s="7"/>
       <c r="K348" s="7"/>
     </row>
-    <row r="349" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="349" spans="1:11">
       <c r="A349" s="5">
         <v>42607</v>
       </c>
@@ -9073,7 +9073,7 @@
       <c r="J349" s="7"/>
       <c r="K349" s="7"/>
     </row>
-    <row r="350" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="350" spans="1:11">
       <c r="A350" s="5">
         <v>42614</v>
       </c>
@@ -9092,7 +9092,7 @@
       <c r="J350" s="7"/>
       <c r="K350" s="7"/>
     </row>
-    <row r="351" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="351" spans="1:11">
       <c r="A351" s="5">
         <v>42621</v>
       </c>
@@ -9111,7 +9111,7 @@
       <c r="J351" s="7"/>
       <c r="K351" s="7"/>
     </row>
-    <row r="352" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="352" spans="1:11">
       <c r="A352" s="5">
         <v>42628</v>
       </c>
@@ -9130,7 +9130,7 @@
       <c r="J352" s="7"/>
       <c r="K352" s="7"/>
     </row>
-    <row r="353" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="353" spans="1:11">
       <c r="A353" s="5">
         <v>42635</v>
       </c>
@@ -9149,7 +9149,7 @@
       <c r="J353" s="7"/>
       <c r="K353" s="7"/>
     </row>
-    <row r="354" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="354" spans="1:11">
       <c r="A354" s="5">
         <v>42642</v>
       </c>
@@ -9168,7 +9168,7 @@
       <c r="J354" s="7"/>
       <c r="K354" s="7"/>
     </row>
-    <row r="355" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="355" spans="1:11">
       <c r="A355" s="5">
         <v>42649</v>
       </c>
@@ -9187,7 +9187,7 @@
       <c r="J355" s="7"/>
       <c r="K355" s="7"/>
     </row>
-    <row r="356" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="356" spans="1:11">
       <c r="A356" s="5">
         <v>42656</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="J356" s="7"/>
       <c r="K356" s="7"/>
     </row>
-    <row r="357" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="357" spans="1:11">
       <c r="A357" s="5">
         <v>42663</v>
       </c>
@@ -9225,7 +9225,7 @@
       <c r="J357" s="7"/>
       <c r="K357" s="7"/>
     </row>
-    <row r="358" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="358" spans="1:11">
       <c r="A358" s="5">
         <v>42670</v>
       </c>
@@ -9244,7 +9244,7 @@
       <c r="J358" s="7"/>
       <c r="K358" s="7"/>
     </row>
-    <row r="359" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="359" spans="1:11">
       <c r="A359" s="5">
         <v>42677</v>
       </c>
@@ -9263,7 +9263,7 @@
       <c r="J359" s="7"/>
       <c r="K359" s="7"/>
     </row>
-    <row r="360" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="360" spans="1:11">
       <c r="A360" s="5">
         <v>42684</v>
       </c>
@@ -9282,7 +9282,7 @@
       <c r="J360" s="7"/>
       <c r="K360" s="7"/>
     </row>
-    <row r="361" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="361" spans="1:11">
       <c r="A361" s="5">
         <v>42691</v>
       </c>
@@ -9301,7 +9301,7 @@
       <c r="J361" s="7"/>
       <c r="K361" s="7"/>
     </row>
-    <row r="362" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="362" spans="1:11">
       <c r="A362" s="5">
         <v>42697</v>
       </c>
@@ -9320,7 +9320,7 @@
       <c r="J362" s="7"/>
       <c r="K362" s="7"/>
     </row>
-    <row r="363" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="363" spans="1:11">
       <c r="A363" s="5">
         <v>42705</v>
       </c>
@@ -9339,7 +9339,7 @@
       <c r="J363" s="7"/>
       <c r="K363" s="7"/>
     </row>
-    <row r="364" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="364" spans="1:11">
       <c r="A364" s="5">
         <v>42712</v>
       </c>
@@ -9358,7 +9358,7 @@
       <c r="J364" s="7"/>
       <c r="K364" s="7"/>
     </row>
-    <row r="365" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="365" spans="1:11">
       <c r="A365" s="5">
         <v>42719</v>
       </c>
@@ -9377,7 +9377,7 @@
       <c r="J365" s="7"/>
       <c r="K365" s="7"/>
     </row>
-    <row r="366" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="366" spans="1:11">
       <c r="A366" s="5">
         <v>42726</v>
       </c>
@@ -9396,7 +9396,7 @@
       <c r="J366" s="7"/>
       <c r="K366" s="7"/>
     </row>
-    <row r="367" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="367" spans="1:11">
       <c r="A367" s="5">
         <v>42733</v>
       </c>
@@ -9415,7 +9415,7 @@
       <c r="J367" s="7"/>
       <c r="K367" s="7"/>
     </row>
-    <row r="368" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="368" spans="1:11">
       <c r="A368" s="5">
         <v>42740</v>
       </c>
@@ -9434,7 +9434,7 @@
       <c r="J368" s="7"/>
       <c r="K368" s="7"/>
     </row>
-    <row r="369" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="369" spans="1:11">
       <c r="A369" s="5">
         <v>42747</v>
       </c>
@@ -9453,7 +9453,7 @@
       <c r="J369" s="7"/>
       <c r="K369" s="7"/>
     </row>
-    <row r="370" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="370" spans="1:11">
       <c r="A370" s="5">
         <v>42754</v>
       </c>
@@ -9472,7 +9472,7 @@
       <c r="J370" s="7"/>
       <c r="K370" s="7"/>
     </row>
-    <row r="371" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="371" spans="1:11">
       <c r="A371" s="5">
         <v>42761</v>
       </c>
@@ -9491,7 +9491,7 @@
       <c r="J371" s="7"/>
       <c r="K371" s="7"/>
     </row>
-    <row r="372" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="372" spans="1:11">
       <c r="A372" s="5">
         <v>42768</v>
       </c>
@@ -9510,7 +9510,7 @@
       <c r="J372" s="7"/>
       <c r="K372" s="7"/>
     </row>
-    <row r="373" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="373" spans="1:11">
       <c r="A373" s="5">
         <v>42775</v>
       </c>
@@ -9529,7 +9529,7 @@
       <c r="J373" s="7"/>
       <c r="K373" s="7"/>
     </row>
-    <row r="374" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="374" spans="1:11">
       <c r="A374" s="5">
         <v>42782</v>
       </c>
@@ -9548,7 +9548,7 @@
       <c r="J374" s="7"/>
       <c r="K374" s="7"/>
     </row>
-    <row r="375" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="375" spans="1:11">
       <c r="A375" s="5">
         <v>42789</v>
       </c>
@@ -9567,7 +9567,7 @@
       <c r="J375" s="7"/>
       <c r="K375" s="7"/>
     </row>
-    <row r="376" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="376" spans="1:11">
       <c r="A376" s="5">
         <v>42796</v>
       </c>
@@ -9586,7 +9586,7 @@
       <c r="J376" s="7"/>
       <c r="K376" s="7"/>
     </row>
-    <row r="377" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="377" spans="1:11">
       <c r="A377" s="5">
         <v>42803</v>
       </c>
@@ -9605,7 +9605,7 @@
       <c r="J377" s="7"/>
       <c r="K377" s="7"/>
     </row>
-    <row r="378" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="378" spans="1:11">
       <c r="A378" s="5">
         <v>42810</v>
       </c>
@@ -9624,7 +9624,7 @@
       <c r="J378" s="7"/>
       <c r="K378" s="7"/>
     </row>
-    <row r="379" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="379" spans="1:11">
       <c r="A379" s="5">
         <v>42817</v>
       </c>
@@ -9643,7 +9643,7 @@
       <c r="J379" s="7"/>
       <c r="K379" s="7"/>
     </row>
-    <row r="380" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="380" spans="1:11">
       <c r="A380" s="5">
         <v>42824</v>
       </c>
@@ -9662,7 +9662,7 @@
       <c r="J380" s="7"/>
       <c r="K380" s="7"/>
     </row>
-    <row r="381" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="381" spans="1:11">
       <c r="A381" s="5">
         <v>42831</v>
       </c>
@@ -9681,7 +9681,7 @@
       <c r="J381" s="7"/>
       <c r="K381" s="7"/>
     </row>
-    <row r="382" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="382" spans="1:11">
       <c r="A382" s="5">
         <v>42838</v>
       </c>
@@ -9700,7 +9700,7 @@
       <c r="J382" s="7"/>
       <c r="K382" s="7"/>
     </row>
-    <row r="383" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="383" spans="1:11">
       <c r="A383" s="5">
         <v>42845</v>
       </c>
@@ -9719,7 +9719,7 @@
       <c r="J383" s="7"/>
       <c r="K383" s="7"/>
     </row>
-    <row r="384" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="384" spans="1:11">
       <c r="A384" s="5">
         <v>42852</v>
       </c>
@@ -9738,7 +9738,7 @@
       <c r="J384" s="7"/>
       <c r="K384" s="7"/>
     </row>
-    <row r="385" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="385" spans="1:11">
       <c r="A385" s="5">
         <v>42859</v>
       </c>
@@ -9757,7 +9757,7 @@
       <c r="J385" s="7"/>
       <c r="K385" s="7"/>
     </row>
-    <row r="386" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="386" spans="1:11">
       <c r="A386" s="5">
         <v>42866</v>
       </c>
@@ -9776,7 +9776,7 @@
       <c r="J386" s="7"/>
       <c r="K386" s="7"/>
     </row>
-    <row r="387" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="387" spans="1:11">
       <c r="A387" s="5">
         <v>42873</v>
       </c>
@@ -9795,7 +9795,7 @@
       <c r="J387" s="7"/>
       <c r="K387" s="7"/>
     </row>
-    <row r="388" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="388" spans="1:11">
       <c r="A388" s="5">
         <v>42880</v>
       </c>
@@ -9814,7 +9814,7 @@
       <c r="J388" s="7"/>
       <c r="K388" s="7"/>
     </row>
-    <row r="389" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="389" spans="1:11">
       <c r="A389" s="5">
         <v>42887</v>
       </c>
@@ -9833,7 +9833,7 @@
       <c r="J389" s="7"/>
       <c r="K389" s="7"/>
     </row>
-    <row r="390" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="390" spans="1:11">
       <c r="A390" s="5">
         <v>42894</v>
       </c>
@@ -9852,7 +9852,7 @@
       <c r="J390" s="7"/>
       <c r="K390" s="7"/>
     </row>
-    <row r="391" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="391" spans="1:11">
       <c r="A391" s="5">
         <v>42901</v>
       </c>
@@ -9871,7 +9871,7 @@
       <c r="J391" s="7"/>
       <c r="K391" s="7"/>
     </row>
-    <row r="392" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="392" spans="1:11">
       <c r="A392" s="5">
         <v>42908</v>
       </c>
@@ -9890,7 +9890,7 @@
       <c r="J392" s="7"/>
       <c r="K392" s="7"/>
     </row>
-    <row r="393" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="393" spans="1:11">
       <c r="A393" s="5">
         <v>42915</v>
       </c>
@@ -9909,7 +9909,7 @@
       <c r="J393" s="7"/>
       <c r="K393" s="7"/>
     </row>
-    <row r="394" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="394" spans="1:11">
       <c r="A394" s="5">
         <v>42922</v>
       </c>
@@ -9928,7 +9928,7 @@
       <c r="J394" s="7"/>
       <c r="K394" s="7"/>
     </row>
-    <row r="395" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="395" spans="1:11">
       <c r="A395" s="5">
         <v>42929</v>
       </c>
@@ -9947,7 +9947,7 @@
       <c r="J395" s="7"/>
       <c r="K395" s="7"/>
     </row>
-    <row r="396" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="396" spans="1:11">
       <c r="A396" s="5">
         <v>42936</v>
       </c>
@@ -9966,7 +9966,7 @@
       <c r="J396" s="7"/>
       <c r="K396" s="7"/>
     </row>
-    <row r="397" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="397" spans="1:11">
       <c r="A397" s="5">
         <v>42943</v>
       </c>
@@ -9985,7 +9985,7 @@
       <c r="J397" s="7"/>
       <c r="K397" s="7"/>
     </row>
-    <row r="398" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="398" spans="1:11">
       <c r="A398" s="5">
         <v>42950</v>
       </c>
@@ -10004,7 +10004,7 @@
       <c r="J398" s="7"/>
       <c r="K398" s="7"/>
     </row>
-    <row r="399" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="399" spans="1:11">
       <c r="A399" s="5">
         <v>42957</v>
       </c>
@@ -10023,7 +10023,7 @@
       <c r="J399" s="7"/>
       <c r="K399" s="7"/>
     </row>
-    <row r="400" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="400" spans="1:11">
       <c r="A400" s="5">
         <v>42964</v>
       </c>
@@ -10042,7 +10042,7 @@
       <c r="J400" s="7"/>
       <c r="K400" s="7"/>
     </row>
-    <row r="401" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="401" spans="1:11">
       <c r="A401" s="5">
         <v>42971</v>
       </c>
@@ -10061,7 +10061,7 @@
       <c r="J401" s="7"/>
       <c r="K401" s="7"/>
     </row>
-    <row r="402" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="402" spans="1:11">
       <c r="A402" s="5">
         <v>42978</v>
       </c>
@@ -10080,7 +10080,7 @@
       <c r="J402" s="7"/>
       <c r="K402" s="7"/>
     </row>
-    <row r="403" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="403" spans="1:11">
       <c r="A403" s="5">
         <v>42985</v>
       </c>
@@ -10099,7 +10099,7 @@
       <c r="J403" s="7"/>
       <c r="K403" s="7"/>
     </row>
-    <row r="404" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="404" spans="1:11">
       <c r="A404" s="5">
         <v>42992</v>
       </c>
@@ -10118,7 +10118,7 @@
       <c r="J404" s="7"/>
       <c r="K404" s="7"/>
     </row>
-    <row r="405" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="405" spans="1:11">
       <c r="A405" s="5">
         <v>42999</v>
       </c>
@@ -10137,7 +10137,7 @@
       <c r="J405" s="7"/>
       <c r="K405" s="7"/>
     </row>
-    <row r="406" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="406" spans="1:11">
       <c r="A406" s="5">
         <v>43006</v>
       </c>
@@ -10156,7 +10156,7 @@
       <c r="J406" s="7"/>
       <c r="K406" s="7"/>
     </row>
-    <row r="407" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="407" spans="1:11">
       <c r="A407" s="5">
         <v>43013</v>
       </c>
@@ -10175,7 +10175,7 @@
       <c r="J407" s="7"/>
       <c r="K407" s="7"/>
     </row>
-    <row r="408" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="408" spans="1:11">
       <c r="A408" s="5">
         <v>43020</v>
       </c>
@@ -10194,7 +10194,7 @@
       <c r="J408" s="7"/>
       <c r="K408" s="7"/>
     </row>
-    <row r="409" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="409" spans="1:11">
       <c r="A409" s="5">
         <v>43027</v>
       </c>
@@ -10213,7 +10213,7 @@
       <c r="J409" s="7"/>
       <c r="K409" s="7"/>
     </row>
-    <row r="410" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="410" spans="1:11">
       <c r="A410" s="5">
         <v>43034</v>
       </c>
@@ -10232,7 +10232,7 @@
       <c r="J410" s="7"/>
       <c r="K410" s="7"/>
     </row>
-    <row r="411" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="411" spans="1:11">
       <c r="A411" s="5">
         <v>43041</v>
       </c>
@@ -10251,7 +10251,7 @@
       <c r="J411" s="7"/>
       <c r="K411" s="7"/>
     </row>
-    <row r="412" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="412" spans="1:11">
       <c r="A412" s="5">
         <v>43048</v>
       </c>
@@ -10270,7 +10270,7 @@
       <c r="J412" s="7"/>
       <c r="K412" s="7"/>
     </row>
-    <row r="413" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="413" spans="1:11">
       <c r="A413" s="5">
         <v>43055</v>
       </c>
@@ -10289,7 +10289,7 @@
       <c r="J413" s="7"/>
       <c r="K413" s="7"/>
     </row>
-    <row r="414" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="414" spans="1:11">
       <c r="A414" s="5">
         <v>43061</v>
       </c>
@@ -10308,7 +10308,7 @@
       <c r="J414" s="7"/>
       <c r="K414" s="7"/>
     </row>
-    <row r="415" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="415" spans="1:11">
       <c r="A415" s="5">
         <v>43069</v>
       </c>
@@ -10327,7 +10327,7 @@
       <c r="J415" s="7"/>
       <c r="K415" s="7"/>
     </row>
-    <row r="416" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="416" spans="1:11">
       <c r="A416" s="5">
         <v>43076</v>
       </c>
@@ -10346,7 +10346,7 @@
       <c r="J416" s="7"/>
       <c r="K416" s="7"/>
     </row>
-    <row r="417" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="417" spans="1:11">
       <c r="A417" s="5">
         <v>43083</v>
       </c>
@@ -10365,7 +10365,7 @@
       <c r="J417" s="7"/>
       <c r="K417" s="7"/>
     </row>
-    <row r="418" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="418" spans="1:11">
       <c r="A418" s="5">
         <v>43090</v>
       </c>
@@ -10384,7 +10384,7 @@
       <c r="J418" s="7"/>
       <c r="K418" s="7"/>
     </row>
-    <row r="419" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="419" spans="1:11">
       <c r="A419" s="5">
         <v>43097</v>
       </c>
@@ -10403,7 +10403,7 @@
       <c r="J419" s="7"/>
       <c r="K419" s="7"/>
     </row>
-    <row r="420" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="420" spans="1:11">
       <c r="A420" s="5">
         <v>43104</v>
       </c>
@@ -10422,7 +10422,7 @@
       <c r="J420" s="7"/>
       <c r="K420" s="7"/>
     </row>
-    <row r="421" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="421" spans="1:11">
       <c r="A421" s="5">
         <v>43111</v>
       </c>
@@ -10441,7 +10441,7 @@
       <c r="J421" s="7"/>
       <c r="K421" s="7"/>
     </row>
-    <row r="422" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="422" spans="1:11">
       <c r="A422" s="5">
         <v>43118</v>
       </c>
@@ -10460,7 +10460,7 @@
       <c r="J422" s="7"/>
       <c r="K422" s="7"/>
     </row>
-    <row r="423" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="423" spans="1:11">
       <c r="A423" s="5">
         <v>43125</v>
       </c>
@@ -10479,7 +10479,7 @@
       <c r="J423" s="7"/>
       <c r="K423" s="7"/>
     </row>
-    <row r="424" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="424" spans="1:11">
       <c r="A424" s="5">
         <v>43132</v>
       </c>
@@ -10498,7 +10498,7 @@
       <c r="J424" s="7"/>
       <c r="K424" s="7"/>
     </row>
-    <row r="425" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="425" spans="1:11">
       <c r="A425" s="5">
         <v>43139</v>
       </c>
@@ -10517,7 +10517,7 @@
       <c r="J425" s="7"/>
       <c r="K425" s="7"/>
     </row>
-    <row r="426" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="426" spans="1:11">
       <c r="A426" s="5">
         <v>43146</v>
       </c>
@@ -10536,7 +10536,7 @@
       <c r="J426" s="7"/>
       <c r="K426" s="7"/>
     </row>
-    <row r="427" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="427" spans="1:11">
       <c r="A427" s="5">
         <v>43153</v>
       </c>
@@ -10555,7 +10555,7 @@
       <c r="J427" s="7"/>
       <c r="K427" s="7"/>
     </row>
-    <row r="428" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="428" spans="1:11">
       <c r="A428" s="5">
         <v>43160</v>
       </c>
@@ -10574,7 +10574,7 @@
       <c r="J428" s="7"/>
       <c r="K428" s="7"/>
     </row>
-    <row r="429" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="429" spans="1:11">
       <c r="A429" s="5">
         <v>43167</v>
       </c>
@@ -10593,7 +10593,7 @@
       <c r="J429" s="7"/>
       <c r="K429" s="7"/>
     </row>
-    <row r="430" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="430" spans="1:11">
       <c r="A430" s="5">
         <v>43174</v>
       </c>
@@ -10612,7 +10612,7 @@
       <c r="J430" s="7"/>
       <c r="K430" s="7"/>
     </row>
-    <row r="431" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="431" spans="1:11">
       <c r="A431" s="5">
         <v>43181</v>
       </c>
@@ -10631,7 +10631,7 @@
       <c r="J431" s="7"/>
       <c r="K431" s="7"/>
     </row>
-    <row r="432" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="432" spans="1:11">
       <c r="A432" s="5">
         <v>43188</v>
       </c>
@@ -10650,7 +10650,7 @@
       <c r="J432" s="7"/>
       <c r="K432" s="7"/>
     </row>
-    <row r="433" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="433" spans="1:11">
       <c r="A433" s="5">
         <v>43195</v>
       </c>
@@ -10669,7 +10669,7 @@
       <c r="J433" s="7"/>
       <c r="K433" s="7"/>
     </row>
-    <row r="434" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="434" spans="1:11">
       <c r="A434" s="5">
         <v>43202</v>
       </c>
@@ -10688,7 +10688,7 @@
       <c r="J434" s="7"/>
       <c r="K434" s="7"/>
     </row>
-    <row r="435" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="435" spans="1:11">
       <c r="A435" s="5">
         <v>43209</v>
       </c>
@@ -10707,7 +10707,7 @@
       <c r="J435" s="7"/>
       <c r="K435" s="7"/>
     </row>
-    <row r="436" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="436" spans="1:11">
       <c r="A436" s="5">
         <v>43216</v>
       </c>
@@ -10726,7 +10726,7 @@
       <c r="J436" s="7"/>
       <c r="K436" s="7"/>
     </row>
-    <row r="437" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="437" spans="1:11">
       <c r="A437" s="5">
         <v>43223</v>
       </c>
@@ -10745,7 +10745,7 @@
       <c r="J437" s="7"/>
       <c r="K437" s="7"/>
     </row>
-    <row r="438" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="438" spans="1:11">
       <c r="A438" s="5">
         <v>43230</v>
       </c>
@@ -10764,7 +10764,7 @@
       <c r="J438" s="7"/>
       <c r="K438" s="7"/>
     </row>
-    <row r="439" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="439" spans="1:11">
       <c r="A439" s="5">
         <v>43237</v>
       </c>
@@ -10783,7 +10783,7 @@
       <c r="J439" s="7"/>
       <c r="K439" s="7"/>
     </row>
-    <row r="440" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="440" spans="1:11">
       <c r="A440" s="5">
         <v>43244</v>
       </c>
@@ -10802,7 +10802,7 @@
       <c r="J440" s="7"/>
       <c r="K440" s="7"/>
     </row>
-    <row r="441" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="441" spans="1:11">
       <c r="A441" s="5">
         <v>43251</v>
       </c>
@@ -10821,7 +10821,7 @@
       <c r="J441" s="7"/>
       <c r="K441" s="7"/>
     </row>
-    <row r="442" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="442" spans="1:11">
       <c r="A442" s="5">
         <v>43258</v>
       </c>
@@ -10840,7 +10840,7 @@
       <c r="J442" s="7"/>
       <c r="K442" s="7"/>
     </row>
-    <row r="443" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="443" spans="1:11">
       <c r="A443" s="5">
         <v>43265</v>
       </c>
@@ -10859,7 +10859,7 @@
       <c r="J443" s="7"/>
       <c r="K443" s="7"/>
     </row>
-    <row r="444" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="444" spans="1:11">
       <c r="A444" s="5">
         <v>43272</v>
       </c>
@@ -10878,7 +10878,7 @@
       <c r="J444" s="7"/>
       <c r="K444" s="7"/>
     </row>
-    <row r="445" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="445" spans="1:11">
       <c r="A445" s="5">
         <v>43279</v>
       </c>
@@ -10897,7 +10897,7 @@
       <c r="J445" s="7"/>
       <c r="K445" s="7"/>
     </row>
-    <row r="446" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="446" spans="1:11">
       <c r="A446" s="5">
         <v>43286</v>
       </c>
@@ -10916,7 +10916,7 @@
       <c r="J446" s="7"/>
       <c r="K446" s="7"/>
     </row>
-    <row r="447" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="447" spans="1:11">
       <c r="A447" s="5">
         <v>43293</v>
       </c>
@@ -10935,7 +10935,7 @@
       <c r="J447" s="7"/>
       <c r="K447" s="7"/>
     </row>
-    <row r="448" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="448" spans="1:11">
       <c r="A448" s="5">
         <v>43300</v>
       </c>
@@ -10954,7 +10954,7 @@
       <c r="J448" s="7"/>
       <c r="K448" s="7"/>
     </row>
-    <row r="449" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="449" spans="1:11">
       <c r="A449" s="5">
         <v>43307</v>
       </c>
@@ -10973,7 +10973,7 @@
       <c r="J449" s="7"/>
       <c r="K449" s="7"/>
     </row>
-    <row r="450" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="450" spans="1:11">
       <c r="A450" s="5">
         <v>43314</v>
       </c>
@@ -10992,7 +10992,7 @@
       <c r="J450" s="7"/>
       <c r="K450" s="7"/>
     </row>
-    <row r="451" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="451" spans="1:11">
       <c r="A451" s="5">
         <v>43321</v>
       </c>
@@ -11011,7 +11011,7 @@
       <c r="J451" s="7"/>
       <c r="K451" s="7"/>
     </row>
-    <row r="452" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="452" spans="1:11">
       <c r="A452" s="5">
         <v>43328</v>
       </c>
@@ -11030,7 +11030,7 @@
       <c r="J452" s="7"/>
       <c r="K452" s="7"/>
     </row>
-    <row r="453" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="453" spans="1:11">
       <c r="A453" s="5">
         <v>43335</v>
       </c>
@@ -11049,7 +11049,7 @@
       <c r="J453" s="7"/>
       <c r="K453" s="7"/>
     </row>
-    <row r="454" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="454" spans="1:11">
       <c r="A454" s="5">
         <v>43342</v>
       </c>
@@ -11068,7 +11068,7 @@
       <c r="J454" s="7"/>
       <c r="K454" s="7"/>
     </row>
-    <row r="455" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="455" spans="1:11">
       <c r="A455" s="5">
         <v>43349</v>
       </c>
@@ -11087,7 +11087,7 @@
       <c r="J455" s="7"/>
       <c r="K455" s="7"/>
     </row>
-    <row r="456" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="456" spans="1:11">
       <c r="A456" s="5">
         <v>43356</v>
       </c>
@@ -11106,7 +11106,7 @@
       <c r="J456" s="7"/>
       <c r="K456" s="7"/>
     </row>
-    <row r="457" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="457" spans="1:11">
       <c r="A457" s="5">
         <v>43363</v>
       </c>
@@ -11125,7 +11125,7 @@
       <c r="J457" s="7"/>
       <c r="K457" s="7"/>
     </row>
-    <row r="458" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="458" spans="1:11">
       <c r="A458" s="5">
         <v>43370</v>
       </c>
@@ -11144,7 +11144,7 @@
       <c r="J458" s="7"/>
       <c r="K458" s="7"/>
     </row>
-    <row r="459" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="459" spans="1:11">
       <c r="A459" s="5">
         <v>43377</v>
       </c>
@@ -11163,7 +11163,7 @@
       <c r="J459" s="7"/>
       <c r="K459" s="7"/>
     </row>
-    <row r="460" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="460" spans="1:11">
       <c r="A460" s="5">
         <v>43384</v>
       </c>
@@ -11182,7 +11182,7 @@
       <c r="J460" s="7"/>
       <c r="K460" s="7"/>
     </row>
-    <row r="461" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="461" spans="1:11">
       <c r="A461" s="5">
         <v>43391</v>
       </c>
@@ -11201,7 +11201,7 @@
       <c r="J461" s="7"/>
       <c r="K461" s="7"/>
     </row>
-    <row r="462" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="462" spans="1:11">
       <c r="A462" s="5">
         <v>43398</v>
       </c>
@@ -11220,7 +11220,7 @@
       <c r="J462" s="7"/>
       <c r="K462" s="7"/>
     </row>
-    <row r="463" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="463" spans="1:11">
       <c r="A463" s="5">
         <v>43405</v>
       </c>
@@ -11239,7 +11239,7 @@
       <c r="J463" s="7"/>
       <c r="K463" s="7"/>
     </row>
-    <row r="464" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="464" spans="1:11">
       <c r="A464" s="5">
         <v>43412</v>
       </c>
@@ -11258,7 +11258,7 @@
       <c r="J464" s="7"/>
       <c r="K464" s="7"/>
     </row>
-    <row r="465" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="465" spans="1:11">
       <c r="A465" s="5">
         <v>43419</v>
       </c>
@@ -11277,7 +11277,7 @@
       <c r="J465" s="7"/>
       <c r="K465" s="7"/>
     </row>
-    <row r="466" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="466" spans="1:11">
       <c r="A466" s="5">
         <v>43425</v>
       </c>
@@ -11296,7 +11296,7 @@
       <c r="J466" s="7"/>
       <c r="K466" s="7"/>
     </row>
-    <row r="467" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="467" spans="1:11">
       <c r="A467" s="5">
         <v>43433</v>
       </c>
@@ -11315,7 +11315,7 @@
       <c r="J467" s="7"/>
       <c r="K467" s="7"/>
     </row>
-    <row r="468" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="468" spans="1:11">
       <c r="A468" s="5">
         <v>43440</v>
       </c>
@@ -11334,7 +11334,7 @@
       <c r="J468" s="7"/>
       <c r="K468" s="7"/>
     </row>
-    <row r="469" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="469" spans="1:11">
       <c r="A469" s="5">
         <v>43447</v>
       </c>
@@ -11353,7 +11353,7 @@
       <c r="J469" s="7"/>
       <c r="K469" s="7"/>
     </row>
-    <row r="470" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="470" spans="1:11">
       <c r="A470" s="5">
         <v>43454</v>
       </c>
@@ -11372,7 +11372,7 @@
       <c r="J470" s="7"/>
       <c r="K470" s="7"/>
     </row>
-    <row r="471" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="471" spans="1:11">
       <c r="A471" s="5">
         <v>43461</v>
       </c>
@@ -11391,7 +11391,7 @@
       <c r="J471" s="7"/>
       <c r="K471" s="7"/>
     </row>
-    <row r="472" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="472" spans="1:11">
       <c r="A472" s="5">
         <v>43468</v>
       </c>
@@ -11410,7 +11410,7 @@
       <c r="J472" s="7"/>
       <c r="K472" s="7"/>
     </row>
-    <row r="473" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="473" spans="1:11">
       <c r="A473" s="5">
         <v>43475</v>
       </c>
@@ -11429,7 +11429,7 @@
       <c r="J473" s="7"/>
       <c r="K473" s="7"/>
     </row>
-    <row r="474" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="474" spans="1:11">
       <c r="A474" s="5">
         <v>43482</v>
       </c>
@@ -11448,7 +11448,7 @@
       <c r="J474" s="7"/>
       <c r="K474" s="7"/>
     </row>
-    <row r="475" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="475" spans="1:11">
       <c r="A475" s="5">
         <v>43489</v>
       </c>
@@ -11467,7 +11467,7 @@
       <c r="J475" s="7"/>
       <c r="K475" s="7"/>
     </row>
-    <row r="476" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="476" spans="1:11">
       <c r="A476" s="5">
         <v>43496</v>
       </c>
@@ -11486,7 +11486,7 @@
       <c r="J476" s="7"/>
       <c r="K476" s="7"/>
     </row>
-    <row r="477" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="477" spans="1:11">
       <c r="A477" s="5">
         <v>43503</v>
       </c>
@@ -11505,7 +11505,7 @@
       <c r="J477" s="7"/>
       <c r="K477" s="7"/>
     </row>
-    <row r="478" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="478" spans="1:11">
       <c r="A478" s="5">
         <v>43510</v>
       </c>
@@ -11524,7 +11524,7 @@
       <c r="J478" s="7"/>
       <c r="K478" s="7"/>
     </row>
-    <row r="479" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="479" spans="1:11">
       <c r="A479" s="5">
         <v>43517</v>
       </c>
@@ -11543,7 +11543,7 @@
       <c r="J479" s="7"/>
       <c r="K479" s="7"/>
     </row>
-    <row r="480" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="480" spans="1:11">
       <c r="A480" s="5">
         <v>43524</v>
       </c>
@@ -11562,7 +11562,7 @@
       <c r="J480" s="7"/>
       <c r="K480" s="7"/>
     </row>
-    <row r="481" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="481" spans="1:11">
       <c r="A481" s="5">
         <v>43531</v>
       </c>
@@ -11581,7 +11581,7 @@
       <c r="J481" s="7"/>
       <c r="K481" s="7"/>
     </row>
-    <row r="482" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="482" spans="1:11">
       <c r="A482" s="5">
         <v>43538</v>
       </c>
@@ -11600,7 +11600,7 @@
       <c r="J482" s="7"/>
       <c r="K482" s="7"/>
     </row>
-    <row r="483" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="483" spans="1:11">
       <c r="A483" s="5">
         <v>43545</v>
       </c>
@@ -11619,7 +11619,7 @@
       <c r="J483" s="7"/>
       <c r="K483" s="7"/>
     </row>
-    <row r="484" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="484" spans="1:11">
       <c r="A484" s="5">
         <v>43552</v>
       </c>
@@ -11638,7 +11638,7 @@
       <c r="J484" s="7"/>
       <c r="K484" s="7"/>
     </row>
-    <row r="485" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="485" spans="1:11">
       <c r="A485" s="5">
         <v>43559</v>
       </c>
@@ -11657,7 +11657,7 @@
       <c r="J485" s="7"/>
       <c r="K485" s="7"/>
     </row>
-    <row r="486" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="486" spans="1:11">
       <c r="A486" s="5">
         <v>43566</v>
       </c>
@@ -11676,7 +11676,7 @@
       <c r="J486" s="7"/>
       <c r="K486" s="7"/>
     </row>
-    <row r="487" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="487" spans="1:11">
       <c r="A487" s="5">
         <v>43573</v>
       </c>
@@ -11695,7 +11695,7 @@
       <c r="J487" s="7"/>
       <c r="K487" s="7"/>
     </row>
-    <row r="488" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="488" spans="1:11">
       <c r="A488" s="5">
         <v>43580</v>
       </c>
@@ -11714,7 +11714,7 @@
       <c r="J488" s="7"/>
       <c r="K488" s="7"/>
     </row>
-    <row r="489" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="489" spans="1:11">
       <c r="A489" s="5">
         <v>43587</v>
       </c>
@@ -11733,7 +11733,7 @@
       <c r="J489" s="7"/>
       <c r="K489" s="7"/>
     </row>
-    <row r="490" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="490" spans="1:11">
       <c r="A490" s="5">
         <v>43594</v>
       </c>
@@ -11752,7 +11752,7 @@
       <c r="J490" s="7"/>
       <c r="K490" s="7"/>
     </row>
-    <row r="491" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="491" spans="1:11">
       <c r="A491" s="5">
         <v>43601</v>
       </c>
@@ -11771,7 +11771,7 @@
       <c r="J491" s="7"/>
       <c r="K491" s="7"/>
     </row>
-    <row r="492" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="492" spans="1:11">
       <c r="A492" s="5">
         <v>43608</v>
       </c>
@@ -11790,7 +11790,7 @@
       <c r="J492" s="7"/>
       <c r="K492" s="7"/>
     </row>
-    <row r="493" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="493" spans="1:11">
       <c r="A493" s="5">
         <v>43615</v>
       </c>
@@ -11809,7 +11809,7 @@
       <c r="J493" s="7"/>
       <c r="K493" s="7"/>
     </row>
-    <row r="494" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="494" spans="1:11">
       <c r="A494" s="5">
         <v>43622</v>
       </c>
@@ -11828,7 +11828,7 @@
       <c r="J494" s="7"/>
       <c r="K494" s="7"/>
     </row>
-    <row r="495" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="495" spans="1:11">
       <c r="A495" s="5">
         <v>43629</v>
       </c>
@@ -11847,7 +11847,7 @@
       <c r="J495" s="7"/>
       <c r="K495" s="7"/>
     </row>
-    <row r="496" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="496" spans="1:11">
       <c r="A496" s="5">
         <v>43636</v>
       </c>
@@ -11866,7 +11866,7 @@
       <c r="J496" s="7"/>
       <c r="K496" s="7"/>
     </row>
-    <row r="497" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="497" spans="1:11">
       <c r="A497" s="5">
         <v>43643</v>
       </c>
@@ -11885,7 +11885,7 @@
       <c r="J497" s="7"/>
       <c r="K497" s="7"/>
     </row>
-    <row r="498" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="498" spans="1:11">
       <c r="A498" s="5">
         <v>43649</v>
       </c>
@@ -11904,7 +11904,7 @@
       <c r="J498" s="7"/>
       <c r="K498" s="7"/>
     </row>
-    <row r="499" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="499" spans="1:11">
       <c r="A499" s="5">
         <v>43657</v>
       </c>
@@ -11923,7 +11923,7 @@
       <c r="J499" s="7"/>
       <c r="K499" s="7"/>
     </row>
-    <row r="500" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="500" spans="1:11">
       <c r="A500" s="5">
         <v>43664</v>
       </c>
@@ -11942,7 +11942,7 @@
       <c r="J500" s="7"/>
       <c r="K500" s="7"/>
     </row>
-    <row r="501" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="501" spans="1:11">
       <c r="A501" s="5">
         <v>43671</v>
       </c>
@@ -11961,7 +11961,7 @@
       <c r="J501" s="7"/>
       <c r="K501" s="7"/>
     </row>
-    <row r="502" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="502" spans="1:11">
       <c r="A502" s="5">
         <v>43678</v>
       </c>
@@ -11980,7 +11980,7 @@
       <c r="J502" s="7"/>
       <c r="K502" s="7"/>
     </row>
-    <row r="503" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="503" spans="1:11">
       <c r="A503" s="5">
         <v>43685</v>
       </c>
@@ -11999,7 +11999,7 @@
       <c r="J503" s="7"/>
       <c r="K503" s="7"/>
     </row>
-    <row r="504" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="504" spans="1:11">
       <c r="A504" s="5">
         <v>43692</v>
       </c>
@@ -12018,7 +12018,7 @@
       <c r="J504" s="7"/>
       <c r="K504" s="7"/>
     </row>
-    <row r="505" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="505" spans="1:11">
       <c r="A505" s="5">
         <v>43699</v>
       </c>
@@ -12037,7 +12037,7 @@
       <c r="J505" s="7"/>
       <c r="K505" s="7"/>
     </row>
-    <row r="506" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="506" spans="1:11">
       <c r="A506" s="5">
         <v>43706</v>
       </c>
@@ -12056,7 +12056,7 @@
       <c r="J506" s="7"/>
       <c r="K506" s="7"/>
     </row>
-    <row r="507" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="507" spans="1:11">
       <c r="A507" s="5">
         <v>43713</v>
       </c>
@@ -12075,7 +12075,7 @@
       <c r="J507" s="7"/>
       <c r="K507" s="7"/>
     </row>
-    <row r="508" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="508" spans="1:11">
       <c r="A508" s="5">
         <v>43720</v>
       </c>
@@ -12094,7 +12094,7 @@
       <c r="J508" s="7"/>
       <c r="K508" s="7"/>
     </row>
-    <row r="509" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="509" spans="1:11">
       <c r="A509" s="5">
         <v>43727</v>
       </c>
@@ -12113,7 +12113,7 @@
       <c r="J509" s="7"/>
       <c r="K509" s="7"/>
     </row>
-    <row r="510" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="510" spans="1:11">
       <c r="A510" s="5">
         <v>43734</v>
       </c>
@@ -12132,7 +12132,7 @@
       <c r="J510" s="7"/>
       <c r="K510" s="7"/>
     </row>
-    <row r="511" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="511" spans="1:11">
       <c r="A511" s="5">
         <v>43741</v>
       </c>
@@ -12151,7 +12151,7 @@
       <c r="J511" s="7"/>
       <c r="K511" s="7"/>
     </row>
-    <row r="512" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="512" spans="1:11">
       <c r="A512" s="5">
         <v>43748</v>
       </c>
@@ -12170,7 +12170,7 @@
       <c r="J512" s="7"/>
       <c r="K512" s="7"/>
     </row>
-    <row r="513" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="513" spans="1:11">
       <c r="A513" s="5">
         <v>43755</v>
       </c>
@@ -12189,7 +12189,7 @@
       <c r="J513" s="7"/>
       <c r="K513" s="7"/>
     </row>
-    <row r="514" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="514" spans="1:11">
       <c r="A514" s="5">
         <v>43762</v>
       </c>
@@ -12208,7 +12208,7 @@
       <c r="J514" s="7"/>
       <c r="K514" s="7"/>
     </row>
-    <row r="515" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="515" spans="1:11">
       <c r="A515" s="5">
         <v>43769</v>
       </c>
@@ -12227,7 +12227,7 @@
       <c r="J515" s="7"/>
       <c r="K515" s="7"/>
     </row>
-    <row r="516" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="516" spans="1:11">
       <c r="A516" s="5">
         <v>43776</v>
       </c>
@@ -12246,7 +12246,7 @@
       <c r="J516" s="7"/>
       <c r="K516" s="7"/>
     </row>
-    <row r="517" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="517" spans="1:11">
       <c r="A517" s="5">
         <v>43783</v>
       </c>
@@ -12265,7 +12265,7 @@
       <c r="J517" s="7"/>
       <c r="K517" s="7"/>
     </row>
-    <row r="518" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="518" spans="1:11">
       <c r="A518" s="5">
         <v>43790</v>
       </c>
@@ -12284,7 +12284,7 @@
       <c r="J518" s="7"/>
       <c r="K518" s="7"/>
     </row>
-    <row r="519" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="519" spans="1:11">
       <c r="A519" s="5">
         <v>43796</v>
       </c>
@@ -12303,7 +12303,7 @@
       <c r="J519" s="7"/>
       <c r="K519" s="7"/>
     </row>
-    <row r="520" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="520" spans="1:11">
       <c r="A520" s="5">
         <v>43804</v>
       </c>
@@ -12322,7 +12322,7 @@
       <c r="J520" s="7"/>
       <c r="K520" s="7"/>
     </row>
-    <row r="521" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="521" spans="1:11">
       <c r="A521" s="5">
         <v>43811</v>
       </c>
@@ -12341,7 +12341,7 @@
       <c r="J521" s="7"/>
       <c r="K521" s="7"/>
     </row>
-    <row r="522" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="522" spans="1:11">
       <c r="A522" s="5">
         <v>43818</v>
       </c>
@@ -12360,7 +12360,7 @@
       <c r="J522" s="7"/>
       <c r="K522" s="7"/>
     </row>
-    <row r="523" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="523" spans="1:11">
       <c r="A523" s="5">
         <v>43825</v>
       </c>
@@ -12379,7 +12379,7 @@
       <c r="J523" s="7"/>
       <c r="K523" s="7"/>
     </row>
-    <row r="524" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="524" spans="1:11">
       <c r="A524" s="5">
         <v>43832</v>
       </c>
@@ -12398,7 +12398,7 @@
       <c r="J524" s="7"/>
       <c r="K524" s="7"/>
     </row>
-    <row r="525" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="525" spans="1:11">
       <c r="A525" s="5">
         <v>43839</v>
       </c>
@@ -12417,7 +12417,7 @@
       <c r="J525" s="7"/>
       <c r="K525" s="7"/>
     </row>
-    <row r="526" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="526" spans="1:11">
       <c r="A526" s="5">
         <v>43846</v>
       </c>
@@ -12436,7 +12436,7 @@
       <c r="J526" s="7"/>
       <c r="K526" s="7"/>
     </row>
-    <row r="527" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="527" spans="1:11">
       <c r="A527" s="5">
         <v>43853</v>
       </c>
@@ -12455,7 +12455,7 @@
       <c r="J527" s="7"/>
       <c r="K527" s="7"/>
     </row>
-    <row r="528" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="528" spans="1:11">
       <c r="A528" s="5">
         <v>43860</v>
       </c>
@@ -12474,7 +12474,7 @@
       <c r="J528" s="7"/>
       <c r="K528" s="7"/>
     </row>
-    <row r="529" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="529" spans="1:11">
       <c r="A529" s="5">
         <v>43867</v>
       </c>
@@ -12493,7 +12493,7 @@
       <c r="J529" s="7"/>
       <c r="K529" s="7"/>
     </row>
-    <row r="530" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="530" spans="1:11">
       <c r="A530" s="5">
         <v>43874</v>
       </c>
@@ -12512,7 +12512,7 @@
       <c r="J530" s="7"/>
       <c r="K530" s="7"/>
     </row>
-    <row r="531" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="531" spans="1:11">
       <c r="A531" s="5">
         <v>43881</v>
       </c>
@@ -12531,7 +12531,7 @@
       <c r="J531" s="7"/>
       <c r="K531" s="7"/>
     </row>
-    <row r="532" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="532" spans="1:11">
       <c r="A532" s="5">
         <v>43888</v>
       </c>
@@ -12550,7 +12550,7 @@
       <c r="J532" s="7"/>
       <c r="K532" s="7"/>
     </row>
-    <row r="533" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="533" spans="1:11">
       <c r="A533" s="5">
         <v>43895</v>
       </c>
@@ -12569,7 +12569,7 @@
       <c r="J533" s="7"/>
       <c r="K533" s="7"/>
     </row>
-    <row r="534" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="534" spans="1:11">
       <c r="A534" s="5">
         <v>43902</v>
       </c>
@@ -12588,7 +12588,7 @@
       <c r="J534" s="7"/>
       <c r="K534" s="7"/>
     </row>
-    <row r="535" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="535" spans="1:11">
       <c r="A535" s="5">
         <v>43909</v>
       </c>
@@ -12607,7 +12607,7 @@
       <c r="J535" s="7"/>
       <c r="K535" s="7"/>
     </row>
-    <row r="536" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="536" spans="1:11">
       <c r="A536" s="5">
         <v>43916</v>
       </c>
@@ -12626,7 +12626,7 @@
       <c r="J536" s="7"/>
       <c r="K536" s="7"/>
     </row>
-    <row r="537" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="537" spans="1:11">
       <c r="A537" s="5">
         <v>43923</v>
       </c>
@@ -12645,7 +12645,7 @@
       <c r="J537" s="7"/>
       <c r="K537" s="7"/>
     </row>
-    <row r="538" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="538" spans="1:11">
       <c r="A538" s="5">
         <v>43930</v>
       </c>
@@ -12664,7 +12664,7 @@
       <c r="J538" s="7"/>
       <c r="K538" s="7"/>
     </row>
-    <row r="539" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="539" spans="1:11">
       <c r="A539" s="5">
         <v>43937</v>
       </c>
@@ -12683,7 +12683,7 @@
       <c r="J539" s="7"/>
       <c r="K539" s="7"/>
     </row>
-    <row r="540" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="540" spans="1:11">
       <c r="A540" s="5">
         <v>43944</v>
       </c>
@@ -12702,7 +12702,7 @@
       <c r="J540" s="7"/>
       <c r="K540" s="7"/>
     </row>
-    <row r="541" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="541" spans="1:11">
       <c r="A541" s="5">
         <v>43951</v>
       </c>
@@ -12721,7 +12721,7 @@
       <c r="J541" s="7"/>
       <c r="K541" s="7"/>
     </row>
-    <row r="542" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="542" spans="1:11">
       <c r="A542" s="5">
         <v>43958</v>
       </c>
@@ -12740,7 +12740,7 @@
       <c r="J542" s="7"/>
       <c r="K542" s="7"/>
     </row>
-    <row r="543" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="543" spans="1:11">
       <c r="A543" s="5">
         <v>43965</v>
       </c>
@@ -12759,7 +12759,7 @@
       <c r="J543" s="7"/>
       <c r="K543" s="7"/>
     </row>
-    <row r="544" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="544" spans="1:11">
       <c r="A544" s="5">
         <v>43972</v>
       </c>
@@ -12778,7 +12778,7 @@
       <c r="J544" s="7"/>
       <c r="K544" s="7"/>
     </row>
-    <row r="545" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="545" spans="1:11">
       <c r="A545" s="5">
         <v>43979</v>
       </c>
@@ -12797,7 +12797,7 @@
       <c r="J545" s="7"/>
       <c r="K545" s="7"/>
     </row>
-    <row r="546" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="546" spans="1:11">
       <c r="A546" s="5">
         <v>43986</v>
       </c>
@@ -12816,7 +12816,7 @@
       <c r="J546" s="7"/>
       <c r="K546" s="7"/>
     </row>
-    <row r="547" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="547" spans="1:11">
       <c r="A547" s="5">
         <v>43993</v>
       </c>
@@ -12835,7 +12835,7 @@
       <c r="J547" s="7"/>
       <c r="K547" s="7"/>
     </row>
-    <row r="548" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="548" spans="1:11">
       <c r="A548" s="5">
         <v>44000</v>
       </c>
@@ -12854,7 +12854,7 @@
       <c r="J548" s="7"/>
       <c r="K548" s="7"/>
     </row>
-    <row r="549" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="549" spans="1:11">
       <c r="A549" s="5">
         <v>44007</v>
       </c>
@@ -12873,7 +12873,7 @@
       <c r="J549" s="7"/>
       <c r="K549" s="7"/>
     </row>
-    <row r="550" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="550" spans="1:11">
       <c r="A550" s="5">
         <v>44014</v>
       </c>
@@ -12892,7 +12892,7 @@
       <c r="J550" s="7"/>
       <c r="K550" s="7"/>
     </row>
-    <row r="551" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="551" spans="1:11">
       <c r="A551" s="5">
         <v>44021</v>
       </c>
@@ -12911,7 +12911,7 @@
       <c r="J551" s="7"/>
       <c r="K551" s="7"/>
     </row>
-    <row r="552" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="552" spans="1:11">
       <c r="A552" s="5">
         <v>44028</v>
       </c>
@@ -12930,7 +12930,7 @@
       <c r="J552" s="7"/>
       <c r="K552" s="7"/>
     </row>
-    <row r="553" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="553" spans="1:11">
       <c r="A553" s="5">
         <v>44035</v>
       </c>
@@ -12949,7 +12949,7 @@
       <c r="J553" s="7"/>
       <c r="K553" s="7"/>
     </row>
-    <row r="554" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="554" spans="1:11">
       <c r="A554" s="5">
         <v>44042</v>
       </c>
@@ -12968,7 +12968,7 @@
       <c r="J554" s="7"/>
       <c r="K554" s="7"/>
     </row>
-    <row r="555" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="555" spans="1:11">
       <c r="A555" s="5">
         <v>44049</v>
       </c>
@@ -12987,7 +12987,7 @@
       <c r="J555" s="7"/>
       <c r="K555" s="7"/>
     </row>
-    <row r="556" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="556" spans="1:11">
       <c r="A556" s="5">
         <v>44056</v>
       </c>
@@ -13006,7 +13006,7 @@
       <c r="J556" s="7"/>
       <c r="K556" s="7"/>
     </row>
-    <row r="557" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="557" spans="1:11">
       <c r="A557" s="5">
         <v>44063</v>
       </c>
@@ -13025,7 +13025,7 @@
       <c r="J557" s="7"/>
       <c r="K557" s="7"/>
     </row>
-    <row r="558" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="558" spans="1:11">
       <c r="A558" s="5">
         <v>44070</v>
       </c>
@@ -13044,7 +13044,7 @@
       <c r="J558" s="7"/>
       <c r="K558" s="7"/>
     </row>
-    <row r="559" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="559" spans="1:11">
       <c r="A559" s="5">
         <v>44077</v>
       </c>
@@ -13063,7 +13063,7 @@
       <c r="J559" s="7"/>
       <c r="K559" s="7"/>
     </row>
-    <row r="560" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="560" spans="1:11">
       <c r="A560" s="5">
         <v>44084</v>
       </c>
@@ -13082,7 +13082,7 @@
       <c r="J560" s="7"/>
       <c r="K560" s="7"/>
     </row>
-    <row r="561" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="561" spans="1:11">
       <c r="A561" s="5">
         <v>44091</v>
       </c>
@@ -13101,7 +13101,7 @@
       <c r="J561" s="7"/>
       <c r="K561" s="7"/>
     </row>
-    <row r="562" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="562" spans="1:11">
       <c r="A562" s="5">
         <v>44098</v>
       </c>
@@ -13120,7 +13120,7 @@
       <c r="J562" s="7"/>
       <c r="K562" s="7"/>
     </row>
-    <row r="563" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="563" spans="1:11">
       <c r="A563" s="5">
         <v>44105</v>
       </c>
@@ -13139,7 +13139,7 @@
       <c r="J563" s="7"/>
       <c r="K563" s="7"/>
     </row>
-    <row r="564" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="564" spans="1:11">
       <c r="A564" s="5">
         <v>44112</v>
       </c>
@@ -13158,7 +13158,7 @@
       <c r="J564" s="7"/>
       <c r="K564" s="7"/>
     </row>
-    <row r="565" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="565" spans="1:11">
       <c r="A565" s="5">
         <v>44119</v>
       </c>
@@ -13177,7 +13177,7 @@
       <c r="J565" s="7"/>
       <c r="K565" s="7"/>
     </row>
-    <row r="566" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="566" spans="1:11">
       <c r="A566" s="5">
         <v>44126</v>
       </c>
@@ -13196,7 +13196,7 @@
       <c r="J566" s="7"/>
       <c r="K566" s="7"/>
     </row>
-    <row r="567" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="567" spans="1:11">
       <c r="A567" s="5">
         <v>44133</v>
       </c>
@@ -13215,7 +13215,7 @@
       <c r="J567" s="7"/>
       <c r="K567" s="7"/>
     </row>
-    <row r="568" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="568" spans="1:11">
       <c r="A568" s="5">
         <v>44140</v>
       </c>
@@ -13234,7 +13234,7 @@
       <c r="J568" s="7"/>
       <c r="K568" s="7"/>
     </row>
-    <row r="569" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="569" spans="1:11">
       <c r="A569" s="5">
         <v>44147</v>
       </c>
@@ -13253,7 +13253,7 @@
       <c r="J569" s="7"/>
       <c r="K569" s="7"/>
     </row>
-    <row r="570" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="570" spans="1:11">
       <c r="A570" s="5">
         <v>44154</v>
       </c>
@@ -13272,7 +13272,7 @@
       <c r="J570" s="7"/>
       <c r="K570" s="7"/>
     </row>
-    <row r="571" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="571" spans="1:11">
       <c r="A571" s="5">
         <v>44160</v>
       </c>
@@ -13291,7 +13291,7 @@
       <c r="J571" s="7"/>
       <c r="K571" s="7"/>
     </row>
-    <row r="572" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="572" spans="1:11">
       <c r="A572" s="5">
         <v>44168</v>
       </c>
@@ -13310,7 +13310,7 @@
       <c r="J572" s="7"/>
       <c r="K572" s="7"/>
     </row>
-    <row r="573" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="573" spans="1:11">
       <c r="A573" s="5">
         <v>44175</v>
       </c>
@@ -13329,7 +13329,7 @@
       <c r="J573" s="7"/>
       <c r="K573" s="7"/>
     </row>
-    <row r="574" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="574" spans="1:11">
       <c r="A574" s="5">
         <v>44182</v>
       </c>
@@ -13348,7 +13348,7 @@
       <c r="J574" s="7"/>
       <c r="K574" s="7"/>
     </row>
-    <row r="575" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="575" spans="1:11">
       <c r="A575" s="5">
         <v>44189</v>
       </c>
@@ -13367,7 +13367,7 @@
       <c r="J575" s="7"/>
       <c r="K575" s="7"/>
     </row>
-    <row r="576" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="576" spans="1:11">
       <c r="A576" s="5">
         <v>44196</v>
       </c>
@@ -13386,7 +13386,7 @@
       <c r="J576" s="7"/>
       <c r="K576" s="7"/>
     </row>
-    <row r="577" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="577" spans="1:11">
       <c r="A577" s="5">
         <v>44203</v>
       </c>
@@ -13405,7 +13405,7 @@
       <c r="J577" s="7"/>
       <c r="K577" s="7"/>
     </row>
-    <row r="578" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="578" spans="1:11">
       <c r="A578" s="5">
         <v>44210</v>
       </c>
@@ -13424,7 +13424,7 @@
       <c r="J578" s="7"/>
       <c r="K578" s="7"/>
     </row>
-    <row r="579" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="579" spans="1:11">
       <c r="A579" s="5">
         <v>44217</v>
       </c>
@@ -13443,7 +13443,7 @@
       <c r="J579" s="7"/>
       <c r="K579" s="7"/>
     </row>
-    <row r="580" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="580" spans="1:11">
       <c r="A580" s="5">
         <v>44224</v>
       </c>
@@ -13462,7 +13462,7 @@
       <c r="J580" s="7"/>
       <c r="K580" s="7"/>
     </row>
-    <row r="581" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="581" spans="1:11">
       <c r="A581" s="5">
         <v>44231</v>
       </c>
@@ -13481,7 +13481,7 @@
       <c r="J581" s="7"/>
       <c r="K581" s="7"/>
     </row>
-    <row r="582" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="582" spans="1:11">
       <c r="A582" s="5">
         <v>44238</v>
       </c>
@@ -13500,7 +13500,7 @@
       <c r="J582" s="7"/>
       <c r="K582" s="7"/>
     </row>
-    <row r="583" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="583" spans="1:11">
       <c r="A583" s="5">
         <v>44245</v>
       </c>
@@ -13519,7 +13519,7 @@
       <c r="J583" s="7"/>
       <c r="K583" s="7"/>
     </row>
-    <row r="584" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="584" spans="1:11">
       <c r="A584" s="5">
         <v>44252</v>
       </c>
@@ -13538,7 +13538,7 @@
       <c r="J584" s="7"/>
       <c r="K584" s="7"/>
     </row>
-    <row r="585" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="585" spans="1:11">
       <c r="A585" s="5">
         <v>44259</v>
       </c>
@@ -13557,7 +13557,7 @@
       <c r="J585" s="7"/>
       <c r="K585" s="7"/>
     </row>
-    <row r="586" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="586" spans="1:11">
       <c r="A586" s="5">
         <v>44266</v>
       </c>
@@ -13576,7 +13576,7 @@
       <c r="J586" s="7"/>
       <c r="K586" s="7"/>
     </row>
-    <row r="587" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="587" spans="1:11">
       <c r="A587" s="5">
         <v>44273</v>
       </c>
@@ -13595,7 +13595,7 @@
       <c r="J587" s="7"/>
       <c r="K587" s="7"/>
     </row>
-    <row r="588" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="588" spans="1:11">
       <c r="A588" s="5">
         <v>44280</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="J588" s="7"/>
       <c r="K588" s="7"/>
     </row>
-    <row r="589" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="589" spans="1:11">
       <c r="A589" s="5">
         <v>44287</v>
       </c>
@@ -13633,7 +13633,7 @@
       <c r="J589" s="7"/>
       <c r="K589" s="7"/>
     </row>
-    <row r="590" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="590" spans="1:11">
       <c r="A590" s="5">
         <v>44294</v>
       </c>
@@ -13652,7 +13652,7 @@
       <c r="J590" s="7"/>
       <c r="K590" s="7"/>
     </row>
-    <row r="591" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="591" spans="1:11">
       <c r="A591" s="5">
         <v>44301</v>
       </c>
@@ -13671,7 +13671,7 @@
       <c r="J591" s="7"/>
       <c r="K591" s="7"/>
     </row>
-    <row r="592" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="592" spans="1:11">
       <c r="A592" s="5">
         <v>44308</v>
       </c>
@@ -13690,7 +13690,7 @@
       <c r="J592" s="7"/>
       <c r="K592" s="7"/>
     </row>
-    <row r="593" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="593" spans="1:11">
       <c r="A593" s="5">
         <v>44315</v>
       </c>
@@ -13709,7 +13709,7 @@
       <c r="J593" s="7"/>
       <c r="K593" s="7"/>
     </row>
-    <row r="594" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="594" spans="1:11">
       <c r="A594" s="5">
         <v>44322</v>
       </c>
@@ -13728,7 +13728,7 @@
       <c r="J594" s="7"/>
       <c r="K594" s="7"/>
     </row>
-    <row r="595" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="595" spans="1:11">
       <c r="A595" s="5">
         <v>44329</v>
       </c>
@@ -13747,7 +13747,7 @@
       <c r="J595" s="7"/>
       <c r="K595" s="7"/>
     </row>
-    <row r="596" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="596" spans="1:11">
       <c r="A596" s="5">
         <v>44336</v>
       </c>
@@ -13766,7 +13766,7 @@
       <c r="J596" s="7"/>
       <c r="K596" s="7"/>
     </row>
-    <row r="597" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="597" spans="1:11">
       <c r="A597" s="5">
         <v>44343</v>
       </c>
@@ -13785,7 +13785,7 @@
       <c r="J597" s="7"/>
       <c r="K597" s="7"/>
     </row>
-    <row r="598" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="598" spans="1:11">
       <c r="A598" s="5">
         <v>44350</v>
       </c>
@@ -13804,7 +13804,7 @@
       <c r="J598" s="7"/>
       <c r="K598" s="7"/>
     </row>
-    <row r="599" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="599" spans="1:11">
       <c r="A599" s="5">
         <v>44357</v>
       </c>
@@ -13823,7 +13823,7 @@
       <c r="J599" s="7"/>
       <c r="K599" s="7"/>
     </row>
-    <row r="600" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="600" spans="1:11">
       <c r="A600" s="5">
         <v>44364</v>
       </c>
@@ -13842,7 +13842,7 @@
       <c r="J600" s="7"/>
       <c r="K600" s="7"/>
     </row>
-    <row r="601" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="601" spans="1:11">
       <c r="A601" s="5">
         <v>44371</v>
       </c>
@@ -13861,7 +13861,7 @@
       <c r="J601" s="7"/>
       <c r="K601" s="7"/>
     </row>
-    <row r="602" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="602" spans="1:11">
       <c r="A602" s="5">
         <v>44378</v>
       </c>
@@ -13880,7 +13880,7 @@
       <c r="J602" s="7"/>
       <c r="K602" s="7"/>
     </row>
-    <row r="603" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="603" spans="1:11">
       <c r="A603" s="5">
         <v>44385</v>
       </c>
@@ -13899,7 +13899,7 @@
       <c r="J603" s="7"/>
       <c r="K603" s="7"/>
     </row>
-    <row r="604" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="604" spans="1:11">
       <c r="A604" s="5">
         <v>44392</v>
       </c>
@@ -13918,7 +13918,7 @@
       <c r="J604" s="7"/>
       <c r="K604" s="7"/>
     </row>
-    <row r="605" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="605" spans="1:11">
       <c r="A605" s="5">
         <v>44399</v>
       </c>
@@ -13937,7 +13937,7 @@
       <c r="J605" s="7"/>
       <c r="K605" s="7"/>
     </row>
-    <row r="606" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="606" spans="1:11">
       <c r="A606" s="5">
         <v>44406</v>
       </c>
@@ -13956,7 +13956,7 @@
       <c r="J606" s="7"/>
       <c r="K606" s="7"/>
     </row>
-    <row r="607" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="607" spans="1:11">
       <c r="A607" s="5">
         <v>44413</v>
       </c>
@@ -13975,7 +13975,7 @@
       <c r="J607" s="7"/>
       <c r="K607" s="7"/>
     </row>
-    <row r="608" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="608" spans="1:11">
       <c r="A608" s="5">
         <v>44420</v>
       </c>
@@ -13994,7 +13994,7 @@
       <c r="J608" s="7"/>
       <c r="K608" s="7"/>
     </row>
-    <row r="609" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="609" spans="1:11">
       <c r="A609" s="5">
         <v>44427</v>
       </c>
@@ -14013,7 +14013,7 @@
       <c r="J609" s="7"/>
       <c r="K609" s="7"/>
     </row>
-    <row r="610" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="610" spans="1:11">
       <c r="A610" s="5">
         <v>44434</v>
       </c>
@@ -14032,7 +14032,7 @@
       <c r="J610" s="7"/>
       <c r="K610" s="7"/>
     </row>
-    <row r="611" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="611" spans="1:11">
       <c r="A611" s="5">
         <v>44441</v>
       </c>
@@ -14051,7 +14051,7 @@
       <c r="J611" s="7"/>
       <c r="K611" s="7"/>
     </row>
-    <row r="612" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="612" spans="1:11">
       <c r="A612" s="5">
         <v>44448</v>
       </c>
@@ -14070,7 +14070,7 @@
       <c r="J612" s="7"/>
       <c r="K612" s="7"/>
     </row>
-    <row r="613" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="613" spans="1:11">
       <c r="A613" s="5">
         <v>44455</v>
       </c>
@@ -14089,7 +14089,7 @@
       <c r="J613" s="7"/>
       <c r="K613" s="7"/>
     </row>
-    <row r="614" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="614" spans="1:11">
       <c r="A614" s="5">
         <v>44462</v>
       </c>
@@ -14108,7 +14108,7 @@
       <c r="J614" s="7"/>
       <c r="K614" s="7"/>
     </row>
-    <row r="615" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="615" spans="1:11">
       <c r="A615" s="5">
         <v>44469</v>
       </c>
@@ -14127,7 +14127,7 @@
       <c r="J615" s="7"/>
       <c r="K615" s="7"/>
     </row>
-    <row r="616" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="616" spans="1:11">
       <c r="A616" s="5">
         <v>44476</v>
       </c>
@@ -14146,7 +14146,7 @@
       <c r="J616" s="7"/>
       <c r="K616" s="7"/>
     </row>
-    <row r="617" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="617" spans="1:11">
       <c r="A617" s="5">
         <v>44483</v>
       </c>
@@ -14165,7 +14165,7 @@
       <c r="J617" s="7"/>
       <c r="K617" s="7"/>
     </row>
-    <row r="618" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="618" spans="1:11">
       <c r="A618" s="5">
         <v>44490</v>
       </c>
@@ -14184,7 +14184,7 @@
       <c r="J618" s="7"/>
       <c r="K618" s="7"/>
     </row>
-    <row r="619" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="619" spans="1:11">
       <c r="A619" s="5">
         <v>44497</v>
       </c>
@@ -14203,7 +14203,7 @@
       <c r="J619" s="7"/>
       <c r="K619" s="7"/>
     </row>
-    <row r="620" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="620" spans="1:11">
       <c r="A620" s="5">
         <v>44504</v>
       </c>
@@ -14222,7 +14222,7 @@
       <c r="J620" s="7"/>
       <c r="K620" s="7"/>
     </row>
-    <row r="621" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="621" spans="1:11">
       <c r="A621" s="5">
         <v>44510</v>
       </c>
@@ -14241,7 +14241,7 @@
       <c r="J621" s="7"/>
       <c r="K621" s="7"/>
     </row>
-    <row r="622" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="622" spans="1:11">
       <c r="A622" s="5">
         <v>44518</v>
       </c>
@@ -14260,7 +14260,7 @@
       <c r="J622" s="7"/>
       <c r="K622" s="7"/>
     </row>
-    <row r="623" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="623" spans="1:11">
       <c r="A623" s="5">
         <v>44524</v>
       </c>
@@ -14279,7 +14279,7 @@
       <c r="J623" s="7"/>
       <c r="K623" s="7"/>
     </row>
-    <row r="624" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="624" spans="1:11">
       <c r="A624" s="5">
         <v>44532</v>
       </c>
@@ -14298,7 +14298,7 @@
       <c r="J624" s="7"/>
       <c r="K624" s="7"/>
     </row>
-    <row r="625" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="625" spans="1:11">
       <c r="A625" s="5">
         <v>44539</v>
       </c>
@@ -14317,7 +14317,7 @@
       <c r="J625" s="7"/>
       <c r="K625" s="7"/>
     </row>
-    <row r="626" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="626" spans="1:11">
       <c r="A626" s="5">
         <v>44546</v>
       </c>
@@ -14336,7 +14336,7 @@
       <c r="J626" s="7"/>
       <c r="K626" s="7"/>
     </row>
-    <row r="627" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="627" spans="1:11">
       <c r="A627" s="5">
         <v>44553</v>
       </c>
@@ -14355,7 +14355,7 @@
       <c r="J627" s="7"/>
       <c r="K627" s="7"/>
     </row>
-    <row r="628" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="628" spans="1:11">
       <c r="A628" s="5">
         <v>44560</v>
       </c>
@@ -14374,7 +14374,7 @@
       <c r="J628" s="7"/>
       <c r="K628" s="7"/>
     </row>
-    <row r="629" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="629" spans="1:11">
       <c r="A629" s="5">
         <v>44567</v>
       </c>
@@ -14393,7 +14393,7 @@
       <c r="J629" s="7"/>
       <c r="K629" s="7"/>
     </row>
-    <row r="630" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="630" spans="1:11">
       <c r="A630" s="5">
         <v>44574</v>
       </c>
@@ -14412,7 +14412,7 @@
       <c r="J630" s="7"/>
       <c r="K630" s="7"/>
     </row>
-    <row r="631" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="631" spans="1:11">
       <c r="A631" s="5">
         <v>44581</v>
       </c>
@@ -14431,7 +14431,7 @@
       <c r="J631" s="7"/>
       <c r="K631" s="7"/>
     </row>
-    <row r="632" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="632" spans="1:11">
       <c r="A632" s="5">
         <v>44588</v>
       </c>
@@ -14450,7 +14450,7 @@
       <c r="J632" s="7"/>
       <c r="K632" s="7"/>
     </row>
-    <row r="633" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="633" spans="1:11">
       <c r="A633" s="5">
         <v>44595</v>
       </c>
@@ -14469,7 +14469,7 @@
       <c r="J633" s="7"/>
       <c r="K633" s="7"/>
     </row>
-    <row r="634" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="634" spans="1:11">
       <c r="A634" s="5">
         <v>44602</v>
       </c>
@@ -14488,7 +14488,7 @@
       <c r="J634" s="7"/>
       <c r="K634" s="7"/>
     </row>
-    <row r="635" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="635" spans="1:11">
       <c r="A635" s="5">
         <v>44609</v>
       </c>
@@ -14507,7 +14507,7 @@
       <c r="J635" s="7"/>
       <c r="K635" s="7"/>
     </row>
-    <row r="636" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="636" spans="1:11">
       <c r="A636" s="5">
         <v>44616</v>
       </c>
@@ -14526,7 +14526,7 @@
       <c r="J636" s="7"/>
       <c r="K636" s="7"/>
     </row>
-    <row r="637" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="637" spans="1:11">
       <c r="A637" s="5">
         <v>44623</v>
       </c>
@@ -14545,7 +14545,7 @@
       <c r="J637" s="7"/>
       <c r="K637" s="7"/>
     </row>
-    <row r="638" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="638" spans="1:11">
       <c r="A638" s="5">
         <v>44630</v>
       </c>
@@ -14564,7 +14564,7 @@
       <c r="J638" s="7"/>
       <c r="K638" s="7"/>
     </row>
-    <row r="639" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="639" spans="1:11">
       <c r="A639" s="5">
         <v>44637</v>
       </c>
@@ -14583,7 +14583,7 @@
       <c r="J639" s="7"/>
       <c r="K639" s="7"/>
     </row>
-    <row r="640" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="640" spans="1:11">
       <c r="A640" s="5">
         <v>44644</v>
       </c>
@@ -14602,7 +14602,7 @@
       <c r="J640" s="7"/>
       <c r="K640" s="7"/>
     </row>
-    <row r="641" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="641" spans="1:11">
       <c r="A641" s="5">
         <v>44651</v>
       </c>
@@ -14621,7 +14621,7 @@
       <c r="J641" s="7"/>
       <c r="K641" s="7"/>
     </row>
-    <row r="642" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="642" spans="1:11">
       <c r="A642" s="5">
         <v>44658</v>
       </c>
@@ -14640,7 +14640,7 @@
       <c r="J642" s="7"/>
       <c r="K642" s="7"/>
     </row>
-    <row r="643" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="643" spans="1:11">
       <c r="A643" s="5">
         <v>44665</v>
       </c>
@@ -14659,7 +14659,7 @@
       <c r="J643" s="7"/>
       <c r="K643" s="7"/>
     </row>
-    <row r="644" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="644" spans="1:11">
       <c r="A644" s="5">
         <v>44672</v>
       </c>
@@ -14678,7 +14678,7 @@
       <c r="J644" s="7"/>
       <c r="K644" s="7"/>
     </row>
-    <row r="645" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="645" spans="1:11">
       <c r="A645" s="5">
         <v>44679</v>
       </c>
@@ -14697,7 +14697,7 @@
       <c r="J645" s="7"/>
       <c r="K645" s="7"/>
     </row>
-    <row r="646" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="646" spans="1:11">
       <c r="A646" s="5">
         <v>44686</v>
       </c>
@@ -14716,7 +14716,7 @@
       <c r="J646" s="7"/>
       <c r="K646" s="7"/>
     </row>
-    <row r="647" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="647" spans="1:11">
       <c r="A647" s="5">
         <v>44693</v>
       </c>
@@ -14735,7 +14735,7 @@
       <c r="J647" s="7"/>
       <c r="K647" s="7"/>
     </row>
-    <row r="648" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="648" spans="1:11">
       <c r="A648" s="5">
         <v>44700</v>
       </c>
@@ -14754,7 +14754,7 @@
       <c r="J648" s="7"/>
       <c r="K648" s="7"/>
     </row>
-    <row r="649" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="649" spans="1:11">
       <c r="A649" s="5">
         <v>44707</v>
       </c>
@@ -14773,7 +14773,7 @@
       <c r="J649" s="7"/>
       <c r="K649" s="7"/>
     </row>
-    <row r="650" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="650" spans="1:11">
       <c r="A650" s="5">
         <v>44714</v>
       </c>
@@ -14792,7 +14792,7 @@
       <c r="J650" s="7"/>
       <c r="K650" s="7"/>
     </row>
-    <row r="651" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="651" spans="1:11">
       <c r="A651" s="5">
         <v>44721</v>
       </c>
@@ -14811,7 +14811,7 @@
       <c r="J651" s="7"/>
       <c r="K651" s="7"/>
     </row>
-    <row r="652" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="652" spans="1:11">
       <c r="A652" s="5">
         <v>44728</v>
       </c>
@@ -14830,7 +14830,7 @@
       <c r="J652" s="7"/>
       <c r="K652" s="7"/>
     </row>
-    <row r="653" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="653" spans="1:11">
       <c r="A653" s="5">
         <v>44735</v>
       </c>
@@ -14849,7 +14849,7 @@
       <c r="J653" s="7"/>
       <c r="K653" s="7"/>
     </row>
-    <row r="654" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="654" spans="1:11">
       <c r="A654" s="5">
         <v>44742</v>
       </c>
@@ -14868,7 +14868,7 @@
       <c r="J654" s="7"/>
       <c r="K654" s="7"/>
     </row>
-    <row r="655" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="655" spans="1:11">
       <c r="A655" s="5">
         <v>44749</v>
       </c>
@@ -14887,7 +14887,7 @@
       <c r="J655" s="7"/>
       <c r="K655" s="7"/>
     </row>
-    <row r="656" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="656" spans="1:11">
       <c r="A656" s="5">
         <v>44756</v>
       </c>
@@ -14906,7 +14906,7 @@
       <c r="J656" s="7"/>
       <c r="K656" s="7"/>
     </row>
-    <row r="657" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="657" spans="1:11">
       <c r="A657" s="5">
         <v>44763</v>
       </c>
@@ -14925,7 +14925,7 @@
       <c r="J657" s="7"/>
       <c r="K657" s="7"/>
     </row>
-    <row r="658" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="658" spans="1:11">
       <c r="A658" s="5">
         <v>44770</v>
       </c>
@@ -14944,7 +14944,7 @@
       <c r="J658" s="7"/>
       <c r="K658" s="7"/>
     </row>
-    <row r="659" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="659" spans="1:11">
       <c r="A659" s="5">
         <v>44777</v>
       </c>
@@ -14963,7 +14963,7 @@
       <c r="J659" s="7"/>
       <c r="K659" s="7"/>
     </row>
-    <row r="660" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="660" spans="1:11">
       <c r="A660" s="5">
         <v>44784</v>
       </c>
@@ -14982,7 +14982,7 @@
       <c r="J660" s="7"/>
       <c r="K660" s="7"/>
     </row>
-    <row r="661" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="661" spans="1:11">
       <c r="A661" s="5">
         <v>44791</v>
       </c>
@@ -15001,7 +15001,7 @@
       <c r="J661" s="7"/>
       <c r="K661" s="7"/>
     </row>
-    <row r="662" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="662" spans="1:11">
       <c r="A662" s="5">
         <v>44798</v>
       </c>
@@ -15020,7 +15020,7 @@
       <c r="J662" s="7"/>
       <c r="K662" s="7"/>
     </row>
-    <row r="663" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="663" spans="1:11">
       <c r="A663" s="5">
         <v>44805</v>
       </c>
@@ -15039,7 +15039,7 @@
       <c r="J663" s="7"/>
       <c r="K663" s="7"/>
     </row>
-    <row r="664" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="664" spans="1:11">
       <c r="A664" s="5">
         <v>44812</v>
       </c>
@@ -15058,7 +15058,7 @@
       <c r="J664" s="7"/>
       <c r="K664" s="7"/>
     </row>
-    <row r="665" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="665" spans="1:11">
       <c r="A665" s="5">
         <v>44819</v>
       </c>
@@ -15077,7 +15077,7 @@
       <c r="J665" s="7"/>
       <c r="K665" s="7"/>
     </row>
-    <row r="666" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="666" spans="1:11">
       <c r="A666" s="5">
         <v>44826</v>
       </c>
@@ -15096,7 +15096,7 @@
       <c r="J666" s="7"/>
       <c r="K666" s="7"/>
     </row>
-    <row r="667" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="667" spans="1:11">
       <c r="A667" s="5">
         <v>44833</v>
       </c>
@@ -15115,7 +15115,7 @@
       <c r="J667" s="7"/>
       <c r="K667" s="7"/>
     </row>
-    <row r="668" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="668" spans="1:11">
       <c r="A668" s="5">
         <v>44840</v>
       </c>
@@ -15134,7 +15134,7 @@
       <c r="J668" s="7"/>
       <c r="K668" s="7"/>
     </row>
-    <row r="669" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="669" spans="1:11">
       <c r="A669" s="5">
         <v>44847</v>
       </c>
@@ -15153,7 +15153,7 @@
       <c r="J669" s="7"/>
       <c r="K669" s="7"/>
     </row>
-    <row r="670" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="670" spans="1:11">
       <c r="A670" s="6">
         <v>44854</v>
       </c>
@@ -15172,7 +15172,7 @@
       <c r="J670" s="7"/>
       <c r="K670" s="7"/>
     </row>
-    <row r="671" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="671" spans="1:11">
       <c r="A671" s="6">
         <v>44861</v>
       </c>
@@ -15191,7 +15191,7 @@
       <c r="J671" s="7"/>
       <c r="K671" s="7"/>
     </row>
-    <row r="672" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="672" spans="1:11">
       <c r="A672" s="6">
         <v>44868</v>
       </c>
@@ -15210,7 +15210,7 @@
       <c r="J672" s="7"/>
       <c r="K672" s="7"/>
     </row>
-    <row r="673" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="673" spans="1:11">
       <c r="A673" s="6">
         <v>44875</v>
       </c>
@@ -15229,7 +15229,7 @@
       <c r="J673" s="7"/>
       <c r="K673" s="7"/>
     </row>
-    <row r="674" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="674" spans="1:11">
       <c r="A674" s="9">
         <v>44882</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="675" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="675" spans="1:11">
       <c r="A675" s="11">
         <v>44888</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="676" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="676" spans="1:11">
       <c r="A676" s="13">
         <v>44896</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="677" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="677" spans="1:11">
       <c r="A677" s="15">
         <v>44903</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="678" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="678" spans="1:11">
       <c r="A678" s="17">
         <v>44910</v>
       </c>
@@ -15284,7 +15284,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="679" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="679" spans="1:11">
       <c r="A679" s="19">
         <v>44917</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="680" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="680" spans="1:11">
       <c r="A680" s="21">
         <v>44924</v>
       </c>
@@ -15306,7 +15306,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="681" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="681" spans="1:11">
       <c r="A681" s="23">
         <v>44931</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="682" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="682" spans="1:11">
       <c r="A682" s="25">
         <v>44938</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="683" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="683" spans="1:11">
       <c r="A683" s="27">
         <v>44945</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="684" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="684" spans="1:11">
       <c r="A684" s="29">
         <v>44952</v>
       </c>
@@ -15350,7 +15350,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="685" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="685" spans="1:11">
       <c r="A685" s="31">
         <v>44959</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="686" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="686" spans="1:11">
       <c r="A686" s="33">
         <v>44966</v>
       </c>
@@ -15372,7 +15372,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="687" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="687" spans="1:11">
       <c r="A687" s="35">
         <v>44973</v>
       </c>
@@ -15383,7 +15383,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="688" spans="1:11" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="688" spans="1:11">
       <c r="A688" s="37">
         <v>44980</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="689" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="689" spans="1:3">
       <c r="A689" s="39">
         <v>44987</v>
       </c>
@@ -15405,7 +15405,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="690" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="690" spans="1:3">
       <c r="A690" s="41">
         <v>44994</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="691" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="691" spans="1:3">
       <c r="A691" s="43">
         <v>45001</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="692" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="692" spans="1:3">
       <c r="A692" s="45">
         <v>45008</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="693" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="693" spans="1:3">
       <c r="A693" s="47">
         <v>45015</v>
       </c>
@@ -15449,7 +15449,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="694" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="694" spans="1:3">
       <c r="A694" s="49">
         <v>45022</v>
       </c>
@@ -15460,7 +15460,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="695" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="695" spans="1:3">
       <c r="A695" s="51">
         <v>45029</v>
       </c>
@@ -15471,7 +15471,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="696" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="696" spans="1:3">
       <c r="A696" s="53">
         <v>45036</v>
       </c>
@@ -15482,7 +15482,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="697" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="697" spans="1:3">
       <c r="A697" s="55">
         <v>45043</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="698" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="698" spans="1:3">
       <c r="A698" s="57">
         <v>45050</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="699" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="699" spans="1:3">
       <c r="A699" s="59">
         <v>45057</v>
       </c>
@@ -15515,7 +15515,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="700" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="700" spans="1:3">
       <c r="A700" s="61">
         <v>45064</v>
       </c>
@@ -15526,7 +15526,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="701" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="701" spans="1:3">
       <c r="A701" s="63">
         <v>45071</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="702" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="702" spans="1:3">
       <c r="A702" s="65">
         <v>45078</v>
       </c>
@@ -15548,7 +15548,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="703" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="703" spans="1:3">
       <c r="A703" s="67">
         <v>45085</v>
       </c>
@@ -15559,7 +15559,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="704" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="704" spans="1:3">
       <c r="A704" s="69">
         <v>45092</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="705" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="705" spans="1:3">
       <c r="A705" s="71">
         <v>45099</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="706" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="706" spans="1:3">
       <c r="A706" s="73">
         <v>45106</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="707" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="707" spans="1:3">
       <c r="A707" s="75">
         <v>45113</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="708" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="708" spans="1:3">
       <c r="A708" s="77">
         <v>45120</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="709" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="709" spans="1:3">
       <c r="A709" s="79">
         <v>45127</v>
       </c>
@@ -15625,7 +15625,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="710" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="710" spans="1:3">
       <c r="A710" s="81">
         <v>45134</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="711" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="711" spans="1:3">
       <c r="A711" s="83">
         <v>45141</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="712" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="712" spans="1:3">
       <c r="A712" s="85">
         <v>45148</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="713" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="713" spans="1:3">
       <c r="A713" s="87">
         <v>45155</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="714" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="714" spans="1:3">
       <c r="A714" s="89">
         <v>45162</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="715" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="715" spans="1:3">
       <c r="A715" s="91">
         <v>45169</v>
       </c>
@@ -15691,7 +15691,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="716" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="716" spans="1:3">
       <c r="A716" s="93">
         <v>45176</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="717" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="717" spans="1:3">
       <c r="A717" s="95">
         <v>45183</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="718" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="718" spans="1:3">
       <c r="A718" s="97">
         <v>45190</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="719" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="719" spans="1:3">
       <c r="A719" s="99">
         <v>45197</v>
       </c>
@@ -15735,7 +15735,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="720" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="720" spans="1:3">
       <c r="A720" s="101">
         <v>45204</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="721" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="721" spans="1:3">
       <c r="A721" s="103">
         <v>45211</v>
       </c>
@@ -15757,7 +15757,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="722" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="722" spans="1:3">
       <c r="A722" s="105">
         <v>45218</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="723" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="723" spans="1:3">
       <c r="A723" s="107">
         <v>45225</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="724" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="724" spans="1:3">
       <c r="A724" s="109">
         <v>45232</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="725" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="725" spans="1:3">
       <c r="A725" s="111">
         <v>45239</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="726" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="726" spans="1:3">
       <c r="A726" s="113">
         <v>45246</v>
       </c>
@@ -15812,7 +15812,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="727" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="727" spans="1:3">
       <c r="A727" s="115">
         <v>45252</v>
       </c>
@@ -15823,7 +15823,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="728" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="728" spans="1:3">
       <c r="A728" s="117">
         <v>45260</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="729" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="729" spans="1:3">
       <c r="A729" s="119">
         <v>45267</v>
       </c>
@@ -15845,7 +15845,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="730" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="730" spans="1:3">
       <c r="A730" s="121">
         <v>45274</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="731" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="731" spans="1:3">
       <c r="A731" s="123">
         <v>45281</v>
       </c>
@@ -15867,7 +15867,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="732" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="732" spans="1:3">
       <c r="A732" s="125">
         <v>45288</v>
       </c>
@@ -15878,7 +15878,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="733" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="733" spans="1:3">
       <c r="A733" s="127">
         <v>45295</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="734" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="734" spans="1:3">
       <c r="A734" s="129">
         <v>45302</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="735" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="735" spans="1:3">
       <c r="A735" s="131">
         <v>45309</v>
       </c>
@@ -15911,7 +15911,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="736" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="736" spans="1:3">
       <c r="A736" s="133">
         <v>45316</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="737" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="737" spans="1:3">
       <c r="A737" s="135">
         <v>45323</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="738" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="738" spans="1:3">
       <c r="A738" s="137">
         <v>45330</v>
       </c>
@@ -15944,7 +15944,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="739" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="739" spans="1:3">
       <c r="A739" s="139">
         <v>45337</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="740" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="740" spans="1:3">
       <c r="A740" s="141">
         <v>45344</v>
       </c>
@@ -15966,7 +15966,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="741" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="741" spans="1:3">
       <c r="A741" s="143">
         <v>45351</v>
       </c>
@@ -15977,7 +15977,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="742" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="742" spans="1:3">
       <c r="A742" s="145">
         <v>45358</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="743" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="743" spans="1:3">
       <c r="A743" s="147">
         <v>45365</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="744" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="744" spans="1:3">
       <c r="A744" s="149">
         <v>45372</v>
       </c>
@@ -16010,7 +16010,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="745" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="745" spans="1:3">
       <c r="A745" s="151">
         <v>45379</v>
       </c>
@@ -16021,7 +16021,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="746" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="746" spans="1:3">
       <c r="A746" s="153">
         <v>45386</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="747" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="747" spans="1:3">
       <c r="A747" s="155">
         <v>45393</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="748" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="748" spans="1:3">
       <c r="A748" s="157">
         <v>45400</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="749" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="749" spans="1:3">
       <c r="A749" s="159">
         <v>45407</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="750" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="750" spans="1:3">
       <c r="A750" s="161">
         <v>45414</v>
       </c>
@@ -16076,7 +16076,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="751" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="751" spans="1:3">
       <c r="A751" s="163">
         <v>45421</v>
       </c>
@@ -16087,7 +16087,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="752" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="752" spans="1:3">
       <c r="A752" s="165">
         <v>45428</v>
       </c>
@@ -16098,7 +16098,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="753" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="753" spans="1:3">
       <c r="A753" s="167">
         <v>45435</v>
       </c>
@@ -16109,7 +16109,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="754" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="754" spans="1:3">
       <c r="A754" s="167">
         <v>45442</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="755" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="755" spans="1:3">
       <c r="A755" s="167">
         <v>45449</v>
       </c>
@@ -16131,7 +16131,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="756" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="756" spans="1:3">
       <c r="A756" s="5">
         <v>45456</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="757" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="757" spans="1:3">
       <c r="A757" s="5">
         <v>45463</v>
       </c>
@@ -16153,7 +16153,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="758" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="758" spans="1:3">
       <c r="A758" s="5">
         <v>45470</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="759" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="759" spans="1:3">
       <c r="A759" s="5">
         <v>45476</v>
       </c>
@@ -16175,7 +16175,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="760" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="760" spans="1:3">
       <c r="A760" s="5">
         <v>45484</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="761" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="761" spans="1:3">
       <c r="A761" s="5">
         <v>45491</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="762" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="762" spans="1:3">
       <c r="A762" s="5">
         <v>45498</v>
       </c>
@@ -16208,7 +16208,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="763" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="763" spans="1:3">
       <c r="A763" s="5">
         <v>45505</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="764" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="764" spans="1:3">
       <c r="A764" s="5">
         <v>45512</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="765" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="765" spans="1:3">
       <c r="A765" s="5">
         <v>45519</v>
       </c>
@@ -16241,7 +16241,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="766" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="766" spans="1:3">
       <c r="A766" s="5">
         <v>45526</v>
       </c>
@@ -16252,7 +16252,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="767" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="767" spans="1:3">
       <c r="A767" s="5">
         <v>45533</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="768" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="768" spans="1:3">
       <c r="A768" s="5">
         <v>45540</v>
       </c>
@@ -16274,7 +16274,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="769" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="769" spans="1:4">
       <c r="A769" s="5">
         <v>45547</v>
       </c>
@@ -16285,7 +16285,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="770" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="770" spans="1:4">
       <c r="A770" s="5">
         <v>45554</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="771" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="771" spans="1:4">
       <c r="A771" s="5">
         <v>45561</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="772" spans="1:4">
       <c r="A772" s="5">
         <v>45568</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="773" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="773" spans="1:4">
       <c r="A773" s="5">
         <v>45575</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="774" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="774" spans="1:4">
       <c r="A774" s="5">
         <v>45582</v>
       </c>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="D774" s="169"/>
     </row>
-    <row r="775" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="775" spans="1:4">
       <c r="A775" s="5">
         <v>45589</v>
       </c>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="D775" s="169"/>
     </row>
-    <row r="776" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="776" spans="1:4">
       <c r="A776" s="5">
         <v>45596</v>
       </c>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="D776" s="169"/>
     </row>
-    <row r="777" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="777" spans="1:4">
       <c r="A777" s="5">
         <v>45603</v>
       </c>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="D777" s="169"/>
     </row>
-    <row r="778" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="778" spans="1:4">
       <c r="A778" s="5">
         <v>45610</v>
       </c>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="D778" s="169"/>
     </row>
-    <row r="779" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="779" spans="1:4">
       <c r="A779" s="5">
         <v>45617</v>
       </c>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="D779" s="169"/>
     </row>
-    <row r="780" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="780" spans="1:4">
       <c r="A780" s="5">
         <v>45623</v>
       </c>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="D780" s="169"/>
     </row>
-    <row r="781" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="781" spans="1:4">
       <c r="A781" s="5">
         <v>45631</v>
       </c>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="D781" s="169"/>
     </row>
-    <row r="782" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="782" spans="1:4">
       <c r="A782" s="5">
         <v>45638</v>
       </c>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="D782" s="169"/>
     </row>
-    <row r="783" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="783" spans="1:4">
       <c r="A783" s="5">
         <v>45645</v>
       </c>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="D783" s="169"/>
     </row>
-    <row r="784" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="784" spans="1:4">
       <c r="A784" s="5">
         <v>45652</v>
       </c>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="D784" s="169"/>
     </row>
-    <row r="785" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="785" spans="1:4">
       <c r="A785" s="5">
         <v>45659</v>
       </c>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="D785" s="169"/>
     </row>
-    <row r="786" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="786" spans="1:4">
       <c r="A786" s="5">
         <v>45666</v>
       </c>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="D786" s="169"/>
     </row>
-    <row r="787" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="787" spans="1:4">
       <c r="A787" s="5">
         <v>45673</v>
       </c>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="D787" s="169"/>
     </row>
-    <row r="788" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="788" spans="1:4">
       <c r="A788" s="5">
         <v>45680</v>
       </c>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="D788" s="169"/>
     </row>
-    <row r="789" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="789" spans="1:4">
       <c r="A789" s="5">
         <v>45687</v>
       </c>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="D789" s="169"/>
     </row>
-    <row r="790" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="790" spans="1:4">
       <c r="A790" s="5">
         <v>45694</v>
       </c>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="D790" s="169"/>
     </row>
-    <row r="791" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="791" spans="1:4">
       <c r="A791" s="5">
         <v>45701</v>
       </c>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="D791" s="169"/>
     </row>
-    <row r="792" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="792" spans="1:4">
       <c r="A792" s="5">
         <v>45708</v>
       </c>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="D792" s="169"/>
     </row>
-    <row r="793" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="793" spans="1:4">
       <c r="A793" s="5">
         <v>45715</v>
       </c>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D793" s="169"/>
     </row>
-    <row r="794" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="794" spans="1:4">
       <c r="A794" s="5">
         <v>45722</v>
       </c>
@@ -16580,7 +16580,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="795" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="795" spans="1:4">
       <c r="A795" s="5">
         <v>45729</v>
       </c>
@@ -16591,7 +16591,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="796" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="796" spans="1:4">
       <c r="A796" s="5">
         <v>45736</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="797" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="797" spans="1:4">
       <c r="A797" s="5">
         <v>45743</v>
       </c>
@@ -16613,7 +16613,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="798" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="798" spans="1:4">
       <c r="A798" s="5">
         <v>45750</v>
       </c>
@@ -16624,7 +16624,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="799" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="799" spans="1:4">
       <c r="A799" s="5">
         <v>45757</v>
       </c>
@@ -16635,7 +16635,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="800" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="800" spans="1:4">
       <c r="A800" s="5">
         <v>45764</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="801" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="801" spans="1:4">
       <c r="A801" s="5">
         <v>45771</v>
       </c>
@@ -16657,7 +16657,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="802" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="802" spans="1:4">
       <c r="A802" s="5">
         <v>45778</v>
       </c>
@@ -16668,7 +16668,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="803" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="803" spans="1:4">
       <c r="A803" s="5">
         <v>45785</v>
       </c>
@@ -16679,7 +16679,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="804" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="804" spans="1:4">
       <c r="A804" s="5">
         <v>45792</v>
       </c>
@@ -16690,7 +16690,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="805" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="805" spans="1:4">
       <c r="A805" s="5">
         <v>45799</v>
       </c>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="D805" s="169"/>
     </row>
-    <row r="806" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="806" spans="1:4">
       <c r="A806" s="5">
         <v>45806</v>
       </c>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D806" s="169"/>
     </row>
-    <row r="807" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="807" spans="1:4">
       <c r="A807" s="5">
         <v>45813</v>
       </c>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="D807" s="169"/>
     </row>
-    <row r="808" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="808" spans="1:4">
       <c r="A808" s="5">
         <v>45820</v>
       </c>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D808" s="169"/>
     </row>
-    <row r="809" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="809" spans="1:4">
       <c r="A809" s="5">
         <v>45826</v>
       </c>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="D809" s="169"/>
     </row>
-    <row r="810" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="810" spans="1:4">
       <c r="A810" s="5">
         <v>45834</v>
       </c>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="D810" s="169"/>
     </row>
-    <row r="811" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="811" spans="1:4">
       <c r="A811" s="5">
         <v>45841</v>
       </c>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="D811" s="169"/>
     </row>
-    <row r="812" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="812" spans="1:4">
       <c r="A812" s="5">
         <v>45848</v>
       </c>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="D812" s="169"/>
     </row>
-    <row r="813" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="813" spans="1:4">
       <c r="A813" s="5">
         <v>45855</v>
       </c>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="D813" s="169"/>
     </row>
-    <row r="814" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="814" spans="1:4">
       <c r="A814" s="5">
         <v>45862</v>
       </c>
@@ -16810,7 +16810,7 @@
       </c>
       <c r="D814" s="169"/>
     </row>
-    <row r="815" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="815" spans="1:4">
       <c r="A815" s="5">
         <v>45869</v>
       </c>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="D815" s="169"/>
     </row>
-    <row r="816" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="816" spans="1:4">
       <c r="A816" s="5">
         <v>45876</v>
       </c>
@@ -16833,7 +16833,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="817" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="817" spans="1:3">
       <c r="A817" s="5">
         <v>45883</v>
       </c>
@@ -16844,7 +16844,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="818" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="818" spans="1:3">
       <c r="A818" s="5">
         <v>45890</v>
       </c>
@@ -16855,7 +16855,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="819" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="819" spans="1:3">
       <c r="A819" s="5">
         <v>45897</v>
       </c>
@@ -16866,7 +16866,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="820" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="820" spans="1:3">
       <c r="A820" s="5">
         <v>45904</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="821" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="821" spans="1:3">
       <c r="A821" s="5">
         <v>45911</v>
       </c>
@@ -16888,7 +16888,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="822" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="822" spans="1:3">
       <c r="A822" s="5">
         <v>45918</v>
       </c>
@@ -16899,7 +16899,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="823" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="823" spans="1:3">
       <c r="A823" s="5">
         <v>45925</v>
       </c>
@@ -16910,7 +16910,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="824" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="824" spans="1:3">
       <c r="A824" s="5">
         <v>45932</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="825" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="825" spans="1:3">
       <c r="A825" s="5">
         <v>45939</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="826" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="826" spans="1:3">
       <c r="A826" s="5">
         <v>45946</v>
       </c>
@@ -16943,7 +16943,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="827" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="827" spans="1:3">
       <c r="A827" s="5">
         <v>45953</v>
       </c>
@@ -16954,7 +16954,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="828" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="828" spans="1:3">
       <c r="A828" s="5">
         <v>45960</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="829" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="829" spans="1:3">
       <c r="A829" s="5">
         <v>45967</v>
       </c>
@@ -16976,7 +16976,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="830" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="830" spans="1:3">
       <c r="A830" s="5">
         <v>45974</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="831" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="831" spans="1:3">
       <c r="A831" s="5">
         <v>45981</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="832" spans="1:3" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="832" spans="1:3">
       <c r="A832" s="5">
         <v>45987</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="833" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="833" spans="1:4">
       <c r="A833" s="5">
         <v>45995</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="834" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="834" spans="1:4">
       <c r="A834" s="5">
         <v>46002</v>
       </c>
@@ -17031,7 +17031,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="835" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="835" spans="1:4">
       <c r="A835" s="5">
         <v>46009</v>
       </c>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="D835" s="169"/>
     </row>
-    <row r="836" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="836" spans="1:4">
       <c r="A836" s="5">
         <v>46015</v>
       </c>
@@ -17055,7 +17055,7 @@
       </c>
       <c r="D836" s="169"/>
     </row>
-    <row r="837" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="837" spans="1:4">
       <c r="A837" s="5">
         <v>46022</v>
       </c>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="D837" s="169"/>
     </row>
-    <row r="838" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="838" spans="1:4">
       <c r="A838" s="5">
         <v>46030</v>
       </c>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="D838" s="169"/>
     </row>
-    <row r="839" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="839" spans="1:4">
       <c r="A839" s="5">
         <v>46037</v>
       </c>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="D839" s="169"/>
     </row>
-    <row r="840" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="840" spans="1:4">
       <c r="A840" s="5">
         <v>46044</v>
       </c>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="D840" s="169"/>
     </row>
-    <row r="841" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="841" spans="1:4">
       <c r="A841" s="5">
         <v>46051</v>
       </c>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="D841" s="169"/>
     </row>
-    <row r="842" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="842" spans="1:4">
       <c r="A842" s="5">
         <v>46058</v>
       </c>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="D842" s="169"/>
     </row>
-    <row r="843" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="843" spans="1:4">
       <c r="A843" s="5">
         <v>46065</v>
       </c>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="D843" s="169"/>
     </row>
-    <row r="844" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="844" spans="1:4">
       <c r="A844" s="5">
         <v>46072</v>
       </c>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="D844" s="169"/>
     </row>
-    <row r="845" spans="1:4" ht="15.9" x14ac:dyDescent="0.65">
+    <row r="845" spans="1:4">
       <c r="A845" s="5">
         <v>46079</v>
       </c>
@@ -17162,6 +17162,126 @@
         <v>5.44</v>
       </c>
       <c r="D845" s="169"/>
+    </row>
+    <row r="846" spans="1:4">
+      <c r="A846" s="5">
+        <v>46079</v>
+      </c>
+      <c r="B846" s="169">
+        <v>5.98</v>
+      </c>
+      <c r="C846" s="169">
+        <v>5.44</v>
+      </c>
+      <c r="D846" s="169"/>
+    </row>
+    <row r="847" spans="1:4">
+      <c r="A847" s="5">
+        <v>46086</v>
+      </c>
+      <c r="B847" s="169">
+        <v>6</v>
+      </c>
+      <c r="C847" s="169">
+        <v>5.43</v>
+      </c>
+      <c r="D847" s="169"/>
+    </row>
+    <row r="848" spans="1:4">
+      <c r="A848" s="5">
+        <v>46093</v>
+      </c>
+      <c r="B848" s="169">
+        <v>6.11</v>
+      </c>
+      <c r="C848" s="169">
+        <v>5.5</v>
+      </c>
+      <c r="D848" s="169"/>
+    </row>
+    <row r="849" spans="1:4">
+      <c r="A849" s="5">
+        <v>46100</v>
+      </c>
+      <c r="B849" s="169">
+        <v>6.22</v>
+      </c>
+      <c r="C849" s="169">
+        <v>5.54</v>
+      </c>
+      <c r="D849" s="169"/>
+    </row>
+    <row r="850" spans="1:4">
+      <c r="A850" s="5">
+        <v>46107</v>
+      </c>
+      <c r="B850" s="169">
+        <v>6.38</v>
+      </c>
+      <c r="C850" s="169">
+        <v>5.75</v>
+      </c>
+      <c r="D850" s="169"/>
+    </row>
+    <row r="851" spans="1:4">
+      <c r="A851" s="5">
+        <v>46114</v>
+      </c>
+      <c r="B851" s="169">
+        <v>6.46</v>
+      </c>
+      <c r="C851" s="169">
+        <v>5.77</v>
+      </c>
+      <c r="D851" s="169"/>
+    </row>
+    <row r="852" spans="1:4">
+      <c r="A852" s="5">
+        <v>46121</v>
+      </c>
+      <c r="B852" s="169">
+        <v>6.37</v>
+      </c>
+      <c r="C852" s="169">
+        <v>5.74</v>
+      </c>
+      <c r="D852" s="169"/>
+    </row>
+    <row r="853" spans="1:4">
+      <c r="A853" s="5">
+        <v>46128</v>
+      </c>
+      <c r="B853" s="169">
+        <v>6.3</v>
+      </c>
+      <c r="C853" s="169">
+        <v>5.65</v>
+      </c>
+      <c r="D853" s="169"/>
+    </row>
+    <row r="854" spans="1:4">
+      <c r="A854" s="5">
+        <v>46135</v>
+      </c>
+      <c r="B854" s="169">
+        <v>6.23</v>
+      </c>
+      <c r="C854" s="169">
+        <v>5.58</v>
+      </c>
+      <c r="D854" s="169"/>
+    </row>
+    <row r="855" spans="1:4">
+      <c r="A855" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B855" s="169">
+        <v>6.3</v>
+      </c>
+      <c r="C855" s="169">
+        <v>5.64</v>
+      </c>
+      <c r="D855" s="169"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLinesSet="0"/>
